--- a/results/phi4_14b/comparison_ToTPlainLLM/ToTPlainLLM_results.xlsx
+++ b/results/phi4_14b/comparison_ToTPlainLLM/ToTPlainLLM_results.xlsx
@@ -723,33 +723,73 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Class Adamax
-------------
-The `Adamax` class implements the Adamax optimization algorithm, which is a variant of the Adam optimizer. 
-Adamax uses the infinity norm for adaptive learning rate scaling, making it suitable for optimizing 
-machine learning models by updating weights based on training data.
-Attributes:
-Methods:
-    __init__(self, learning_rate=0.001, beta_1=0.9, beta_2=0.999, epsilon=1e-07, name='Adamax', **kwargs):
-        Initializes the Adamax optimizer with the specified hyperparameters.
-        Parameters:
-    _create_slots(self, var_list):
-        Creates slots for the optimizer's variables.
-        Parameters:
-    _prepare_local(self, var_device, var_dtype, apply_state):
-        Prepares local variables for applying updates.
-        Parameters:
-    _resource_apply_dense(self, grad, var, apply_state=None):
-        Applies the optimizer update to dense tensors.
-        Parameters:
+          <t>"""
+        Initializes the Adamax optimizer.
+        Args:
+        """
+        super(Adamax, self).__init__(name, **kwargs)
+        """
+        Creates slots for the first moment vector 'm' and the infinity norm 'v'.
+        Args:
+        """
+        """
+        Prepares local variables for applying gradients.
+        Args:
+        """
+        super(Adamax, self)._prepare_local(var_device, var_dtype, apply_state)
+        local_step = math_ops.cast(self.iterations + 1, var_dtype)
+        beta_1_t = array_ops.identity(self._get_hyper('beta_1', var_dtype))
+        beta_2_t = array_ops.identity(self._get_hyper('beta_2', var_dtype))
+        beta_1_power = math_ops.pow(beta_1_t, local_step)
+        lr_t = apply_state[var_device, var_dtype]['lr_t']
+        apply_state[var_device, var_dtype].update(dict(
+            neg_scaled_lr=-lr_t / (1 - beta_1_power),
+            epsilon=tensor_conversion.convert_to_tensor_v2_with_dispatch(self.epsilon, var_dtype),
+            beta_1_t=beta_1_t,
+            beta_1_power=beta_1_power,
+            one_minus_beta_1_t=1 - beta_1_t,
+            beta_2_t=beta_2_t,
+            zero=array_ops.zeros((), dtype=dtypes.int64)
+        ))
+        """
+        Applies dense gradient updates to variables using Adamax optimization.
+        Args:
         Returns:
-    _resource_apply_sparse(self, grad, var, indices, apply_state=None):
-        Applies the optimizer update to sparse tensors.
-        Parameters:
+            Operation that applies the gradient update.
+        """
+        var_device, var_dtype = (var.device, var.dtype.base_dtype)
+        coefficients = (apply_state or {}).get((var_device, var_dtype)) or self._fallback_apply_state(var_device, var_dtype)
+        m = self.get_slot(var, 'm')
+        v = self.get_slot(var, 'v')
+            var=var.handle,
+            m=m.handle,
+            v=v.handle,
+            beta1_power=coefficients['beta_1_power'],
+            lr=coefficients['lr_t'],
+            beta1=coefficients['beta_1_t'],
+            beta2=coefficients['beta_2_t'],
+            epsilon=coefficients['epsilon'],
+            grad=grad,
+            use_locking=self._use_locking
+        )
+        """
+        Applies sparse gradient updates to variables using Adamax optimization.
+        Args:
         Returns:
-    get_config(self):
-        Returns the configuration of the optimizer.
-        Returns:</t>
+            Operation that applies the gradient update.
+        """
+        var_device, var_dtype = (var.device, var.dtype.base_dtype)
+        coefficients = (apply_state or {}).get((var_device, var_dtype)) or self._fallback_apply_state(var_device, var_dtype)
+        m = self.get_slot(var, 'm')
+        m_slice = array_ops.gather(m, indices, axis=coefficients['zero'])
+        m_t_slice = m_slice * coefficients['beta_1_t'] + grad * coefficients['one_minus_beta_1_t']
+            m_t = self._resource_scatter_update(m, indices, m_t_slice)
+        v = self.get_slot(var, 'v')
+        v_slice = array_ops.gather(v, indices, axis=coefficients['zero'])
+        v_t_slice = math_ops.maximum(v_slice * coefficients['beta_2_t'], math_ops.abs(grad))
+            v_t = self._resource_scatter_update(v, indices, v_t_slice)
+        var_slice = coefficients['neg_scaled_lr'] * (m_t_slice / (v_t_slice + coefficients['epsilon']))
+            var_update = self._resource_scatter_add(var, indices, var_slice)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -866,30 +906,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AgglomerationTransform
-This class is a transformer that implements the agglomeration process within the scikit-learn framework. It is designed to aggregate data points based on specified cluster labels, enabling transformation and inverse transformation of datasets. The class extends `TransformerMixin`, making it compatible with scikit-learn's pipeline and model selection utilities.
-Attributes:
-Methods:
-    transform(self, X):
-        Transforms the input data `X` by aggregating features according to specified `labels_` and a `pooling_func`. It supports both sparse and dense data formats.
-        Parameters:
-                The input data to be transformed.
-        Returns:
-                The transformed data where features are pooled/aggregated per cluster. The transformation is conducted using a specified pooling function, defaulting to the mean for dense matrices.
-        Raises:
-    inverse_transform(self, X=None, *, Xt=None):
-        Reverts the transformation applied by the `transform` method, mapping the pooled data back to the original feature space based on `labels_`.
-        Parameters:
-                The transformed data to be inverted. If not provided, `Xt` must be used.
-                Deprecated alias for `X`. If `X` is not provided, this parameter is used.
-        Returns:
-            array-like of shape (n_samples, n_features)
-                The data reverted to its original feature space, using the unique cluster labels to map back to the original feature indices.
-        Raises:
-Notes:
-    - The `transform` method uses a pooling function, which defaults to `np.mean`, to aggregate data points within each cluster. For sparse data, a different aggregation method may be applied.
-    - The `inverse_transform` method is used to reverse the transformation, assuming that the original feature space can be reconstructed from the pooled data.
-    - This class requires `labels_` to be set, which typically means it should be used in conjunction with a clustering algorithm that provides cluster labels.</t>
+          <t>A transformer class that applies an agglomerative transformation to input data.
+    This class provides methods for transforming and inversely transforming datasets 
+    using a specified pooling function, typically used in hierarchical clustering contexts. 
+    Attributes:
+            transform behavior.
+    Methods:
+    1. transform(X):
+       - Parameters:
+       - Returns:
+                       aggregated feature representation according to the specified pooling function.
+       - Raises:
+    2. inverse_transform(X=None, *, Xt=None):
+       - Parameters:
+       - Returns:
+       - Raises:
+    Sub-tasks:
+    1. Initialization and Metadata Setup:
+       - Initializes class attributes, including metadata for inverse transform behavior.
+       - Sets up necessary configurations or defaults required by the transformer methods.
+    2. Transformation Process:
+       - Validates input data `X` to ensure it meets requirements using `_validate_data`.
+       - Applies a specified pooling function (e.g., mean) if conditions are met; otherwise, uses a general approach.
+       - Aggregates samples based on labels and returns the transformed dataset.
+    3. Inverse Transformation Process:
+       - Handles deprecated parameters for backward compatibility using `_deprecate_Xt_in_inverse_transform`.
+       - Validates that the model is fitted before proceeding with inverse transformation.
+       - Utilizes unique label mapping to reconstruct and return the original dataset structure.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -1101,21 +1144,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Perform average pooling over a 1D input using a 2D pooling approach.
-    The `AveragePooling1D` class is a subclass of `Pooling1D` and is specifically designed to apply an average pooling operation over a 1D input. This is achieved by using a 2D pooling operation through the `backend.pool2d` function with the `pool_mode` set to `'avg'`.
-    Attributes:
-    Example:
-        To instantiate and use the `AveragePooling1D` class:
-        ```python
-        # Define input shape
-        input_data = np.random.rand(1, 10, 3)  # Batch size of 1, 10 steps, 3 channels
-        # Create an input layer
-        input_layer = Input(shape=(10, 3))
-        # Apply AveragePooling1D
-        pooling_layer = AveragePooling1D(pool_size=2, padding='same')(input_layer)
-        # Inspect the shape of the pooled output
-        ```
-    The `AveragePooling1D` class is particularly useful in scenarios where reducing the dimensionality of 1D inputs (like time series data) is necessary, while maintaining the temporal structure through pooling operations.</t>
+          <t>Perform average pooling on 1-dimensional input data.
+    This class inherits from `Pooling1D` and is designed to reduce the spatial dimensions of input data by computing
+    the average over specified windows. It uses a specialized method for handling 2D pooling operations internally, 
+    specifically configured for averaging, making it suitable for use in neural network architectures like CNNs.
+    Parameters
+    ----------
+        Size of the pooling window. If an integer is provided, the same value is used for all dimensions except 
+        Strides of the pooling operation. Defaults to `pool_size` if not provided. This parameter controls the 
+        downsampling factor by defining how far the pooling window moves after each operation.
+        Type of padding algorithm to use:
+        The ordering of dimensions in the input:
+    **kwargs
+        Additional keyword arguments passed to the `Pooling1D` base class.
+    Examples
+    --------
+    &gt;&gt;&gt; from keras.layers import AveragePooling1D
+    # Example of creating an AveragePooling1D layer with a pool size of 2 and default stride
+    &gt;&gt;&gt; avg_pool = AveragePooling1D(pool_size=2)
+    Notes
+    -----
+    This class is particularly useful for reducing the spatial dimensions in neural network layers while preserving 
+    important features, thereby helping to reduce computational load and prevent overfitting.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -1327,13 +1377,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A class to perform 2D average pooling, a common operation in convolutional neural networks (CNNs) to downsample the input feature map by averaging over a specified window size.
-    This class is a subclass of `Pooling2D` and implements the specific logic for average pooling.
-    Attributes:
-    Methods:
-    The `AveragePooling2D` layer reduces the spatial dimensions of the input by averaging the values within each pooling window. This helps in reducing computational complexity and controlling overfitting in CNNs.
-    Example:
-        &gt;&gt;&gt; avg_pool_layer = AveragePooling2D(pool_size=(2, 2), strides=(2, 2), padding='same')</t>
+          <t>A class for performing average pooling on 2D inputs.
+    This class extends the `Pooling2D` base class and implements the specific functionality 
+    of average pooling. It reduces the spatial dimensions (i.e., width and height) of a given input 
+    tensor by averaging values within each pooling window defined by the specified pool size, stride, 
+    and padding options.
+    Parameters
+    ----------
+        The size of the average pooling windows for each dimension of the inputs. If only one integer is provided,
+        it will be used for both dimensions.
+        Strides between successive pooling windows. If not specified, it defaults to `pool_size`.
+        One of `"valid"` or `"same"`. `"valid"` means no padding is applied. `"same"` results in padding the input such 
+        that the output has the same height/width dimension as the original input when strides are 1.
+        A string, one of `channels_last` (default) or `channels_first`. The ordering of the dimensions in the inputs. 
+        `channels_last` corresponds to inputs with shape `(batch_size, height, width, channels)` while 
+        `channels_first` corresponds to inputs with shape `(batch_size, channels, height, width)`.
+        Additional arguments that can be passed to the parent class.
+    Methods
+    -------
+    __call__(inputs)
+        Applies average pooling on the input tensor.
+    Returns
+    -------
+    Tensor
+        The output of applying average pooling to the input tensor. The shape depends on the `pool_size`, 
+        `strides`, and `padding` parameters, with dimensions reduced according to these settings.
+    Examples
+    --------
+    &gt;&gt;&gt; avg_pooling_layer = AveragePooling2D()
+    &gt;&gt;&gt; output = avg_pooling_layer(input_tensor)
+    &gt;&gt;&gt; avg_pooling_layer = AveragePooling2D(pool_size=(3, 3), strides=(2, 2))
+    &gt;&gt;&gt; output = avg_pooling_layer(input_tensor)
+    &gt;&gt;&gt; avg_pooling_layer = AveragePooling2D(padding='same')
+    &gt;&gt;&gt; output = avg_pooling_layer(input_tensor)
+    Notes
+    -----
+    - `input_tensor` should be a 4D tensor with shape (batch_size, height, width, channels) 
+      when using the default 'channels_last' data_format.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -1469,28 +1549,31 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AveragePooling3D performs 3D average pooling on the input data.
-    This class provides a 3D version of average pooling, which reduces the spatial dimensions 
-    (depth, height, width) of the input by taking the average over the window defined by the 
-    pool size. It is useful for downsampling and reducing the computational cost of the model.
-    Parameters:
-    -----------
-        Specifies the size of the pooling window for each dimension (depth, height, width).
-        Specifies the strides of the pooling window for each dimension. If None, it defaults to pool_size.
-        One of 'valid' or 'same'. 'valid' means no padding, while 'same' results in padding the input 
-        such that the output has the same dimensions as the input when strides are 1.
-        A string, one of `channels_last` (default) or `channels_first`. It defaults to the image data 
-        format convention used by your Keras config file.
-    **kwargs : 
-        Additional keyword arguments passed to the parent class.
-    Example Usage:
-    --------------
-    ```python
-    # Create an instance of AveragePooling3D
-    avg_pool = AveragePooling3D(pool_size=(2, 2, 2), strides=(2, 2, 2), padding='valid')
-    # Sample input data
-    # Apply average pooling
-    output_data = avg_pool(input_data)</t>
+          <t>Perform 3D average pooling on input data.
+    The `AveragePooling3D` class implements a 3D version of average pooling which downsamples an input volume along its spatial dimensions. It is commonly used in convolutional neural networks to reduce the dimensionality and computational complexity of volumetric data such as 3D images or video sequences. This operation computes the mean value over local neighborhoods defined by the pool size.
+    Attributes:
+                                 If a single integer is provided, it will be uniformly applied across all dimensions.
+                                          Defaults to `pool_size` if not specified.
+                       - `"valid"` indicates no padding is added, and only valid regions are considered for pooling.
+                       - `"same"` ensures that the output dimensions match the input dimensions when strides are 1 by applying necessary padding.
+                                     Acceptable values are `channels_last` or `channels_first`. Defaults to None,
+                                     which uses the Keras configuration setting.
+    Methods:
+        __init__(pool_size=(2, 2, 2), strides=None, padding='valid', data_format=None, **kwargs): 
+            Initialize an instance of the AveragePooling3D layer with specified parameters.
+    """
+        """
+        Initialize a 3D Average Pooling layer.
+        Args:
+                                      Default is (2, 2, 2). If a single integer is provided, it applies uniformly across all dimensions.
+                                              Defaults to `pool_size` if not specified.
+                           - `"valid"` indicates no padding and only valid regions are used for pooling.
+                           - `"same"` ensures the output dimensions match input dimensions when strides are 1 by applying necessary padding.
+                              Default is 'valid'.
+                                         Acceptable values are `channels_last` or `channels_first`. Defaults to None,
+                                         which uses the Keras configuration setting.
+        Returns:
+            None</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2483,73 +2566,63 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bayesian Gaussian Mixture Model.
-    This class implements a Bayesian version of the Gaussian Mixture Model (GMM), 
-    which fits a mixture of Gaussian distributions to data using Bayesian inference. 
-    The model provides flexible modeling and uncertainty quantification by incorporating 
-    Bayesian priors into the parameter estimation process.
-    Parameters
-    ----------
-        The number of mixture components.
-        The type of covariance parameters to use:
-        The convergence threshold. EM iterations will stop when the 
-        lower bound average gain is below this threshold.
-        Non-negative regularization added to the diagonal of covariance matrices.
-        The maximum number of EM iterations to perform.
-        The number of initializations to perform. The best results are kept.
-        Method used to initialize the weights, means, and precisions:
-        The type of prior used on the weights.
-        The concentration parameter for the prior on the weights.
-        The precision parameter for the prior on the means.
-        The prior mean for the means of the components.
-        The degrees of freedom parameter for the prior on the covariances.
-        The prior covariance matrix or vector.
-        Controls the randomness of the initialization.
-        If True, the solution of the last fitting is used as initialization for the next call of fit.
-        Verbosity level.
-        Number of iterations between two consecutive outputs of the lower bound.
+          <t>A Bayesian Gaussian Mixture Model (BGMM) that provides probabilistic clustering.
+    This model extends the standard Gaussian Mixture Model (GMM) by incorporating 
+    prior distributions over parameters, allowing for more flexible and robust 
+    estimation. It is suitable for clustering tasks, density estimation, and as a 
+    generative model.
+    Inherits from:
+        BaseMixture
     Attributes
     ----------
-        Weights of each mixture component.
-        Means of each mixture component.
-        Covariances of each mixture component. The shape depends on `covariance_type`.
-        Cholesky decomposition of the precision matrices.
+        Constraints on initialization parameters with types and allowed values.
     Methods
     -------
-    fit(X)
-        Fit the model to the data matrix X.
-    predict(X)
-        Perform classification on the data X.
-    predict_proba(X)
-        Perform soft classification on the data X.
-    sample(n_samples=1)
-        Generate random samples from the model.
-    _check_parameters(X)
-        Check the parameters of the model.
-    _initialize(X, resp)
-        Initialize the model parameters.
-    _m_step(X, log_resp)
-        Perform the M-step of the EM algorithm.
-    _estimate_log_prob(X)
-        Estimate the log probability of the data under the model.
-    _compute_lower_bound(log_resp, log_prob_norm)
-        Compute the lower bound of the log likelihood.
-    _get_parameters()
-        Get the model parameters.
-    _set_parameters(params)
-        Set the model parameters.
-    Notes
-    -----
-    This implementation is based on the Expectation-Maximization (EM) algorithm 
-    and incorporates Bayesian priors to provide more robust estimates.
-    Examples
-    --------
-    &gt;&gt;&gt; from sklearn.mixture import BayesianGaussianMixture
-    &gt;&gt;&gt; import numpy as np
-    &gt;&gt;&gt; X = np.random.rand(100, 2)
-    &gt;&gt;&gt; model = BayesianGaussianMixture(n_components=3)
-    &gt;&gt;&gt; model.fit(X)
-    &gt;&gt;&gt; labels = model.predict(X)</t>
+    __init__(self, *, n_components=1, covariance_type='full', tol=0.001, reg_covar=1e-06, 
+             max_iter=100, n_init=1, init_params='kmeans', weight_concentration_prior_type='dirichlet_process',
+             weight_concentration_prior=None, mean_precision_prior=None, mean_prior=None,
+             degrees_of_freedom_prior=None, covariance_prior=None, random_state=None, warm_start=False, 
+             verbose=0, verbose_interval=10)
+        Initialize the BayesianGaussianMixture with specified parameters.
+    _check_parameters(self, X)
+        Validate and set model parameters based on input data `X`.
+    _check_weights_parameters(self)
+        Set or validate the weight concentration prior. If not provided,
+        defaults to `1.0 / n_components`.
+    _check_means_parameters(self, X)
+        Set or validate the mean precision and mean priors based on input data `X`.
+        Defaults for mean_prior are computed from `X`, and for
+        mean_precision_prior is set to 1.0 if not provided.
+    _check_precision_parameters(self, X)
+        Set or validate the degrees of freedom prior based on input data `X`.
+        Ensures it's greater than `n_features - 1`.
+    _checkcovariance_prior_parameter(self, X)
+        Set or validate the covariance prior based on input data `X` and
+        specified covariance type. Defaults are derived from `X`.
+    _initialize(self, X, resp)
+        Initialize model parameters using responsibilities `resp` for data `X`.
+    _estimate_weights(self, nk)
+        Estimate weight concentrations from component sizes `nk`. Handles both 
+        Dirichlet process and Dirichlet distribution types.
+    _estimate_means(self, nk, xk)
+        Estimate means of the Gaussian components based on weighted sums.
+    _estimate_precisions(self, nk, xk, sk)
+        Estimate precision matrices or scalars for different covariance types.
+    _m_step(self, X, log_resp)
+        Perform M-step updates for model parameters using data `X` and 
+        logarithmic responsibilities `log_resp`.
+    _estimate_log_weights(self)
+        Compute the logarithm of the weights for each component, considering
+        Dirichlet process or distribution types.
+    _estimate_log_prob(self, X)
+        Estimate the log probability of each sample in `X` under the current model.
+    _compute_lower_bound(self, log_resp, log_prob_norm)
+        Compute the lower bound on the log-likelihood of the data given model parameters.
+    _get_parameters(self)
+        Retrieve all current model parameters as a tuple for use or storage.
+    _set_parameters(self, params)
+        Set model parameters from a provided tuple `params`. Updates internal
+        weights and precision matrices accordingly.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3082,7 +3155,31 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Custom convolutional layer inspired by TensorFlow's Keras API.
+    This class implements a versatile convolutional layer capable of performing 
+    1D, 2D, or 3D convolutions. It allows customization through parameters such as 
+    the number of filters, kernel size, strides, padding, and more. The layer can be 
+    integrated into neural networks for feature extraction and transformation tasks.
+    Attributes:
+            or a tuple specifying dimensions per axis.
+            padding values. Default is 'valid'.
+            the layer (its "activation").
+    Methods:
+        __init__(rank, filters, kernel_size, strides=1, padding='valid', data_format=None, dilation_rate=1, groups=1, activation=None, use_bias=True, kernel_initializer='glorot_uniform', bias_initializer='zeros', kernel_regularizer=None, bias_regularizer=None, activity_regularizer=None, kernel_constraint=None, bias_constraint=None, trainable=True, name=None, conv_op=None, **kwargs):
+            Initializes the Conv layer with specified parameters.
+        build(input_shape):
+            Creates the layer's weights based on the input shape.
+        call(inputs, *args, **kwargs):
+            Performs the convolution operation and returns the output tensor.
+        compute_output_shape(input_shape):
+            Computes the output shape of the layer given an input shape.
+        get_config():
+            Returns a Python dictionary containing the configuration of the layer.
+    Raises:
+                    incompatible kernel size or strides, etc.
+    Example:
+        &gt;&gt;&gt; conv_layer = Conv(rank=2, filters=32, kernel_size=(3, 3))
+        &gt;&gt;&gt; output = conv_layer(inputs)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3298,7 +3395,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>1. Overview
+    The `Conv1D` layer performs a one-dimensional convolution operation on input data, making it suitable for processing sequential or time-series data. This class extends the `Conv` base class by specifying that the convolution rank is set to 1.
+    2. Initialization
+    Parameters:
+    3. Attributes
+    After building the layer, the following attributes are available:
+    4. Usage
+    Example usage within a Keras Sequential model:
+    ```python
+    model = tf.keras.Sequential([
+        tf.keras.layers.Conv1D(filters=32, kernel_size=3, activation='relu', input_shape=(128, 1)),
+        tf.keras.layers.MaxPooling1D(pool_size=2),
+        tf.keras.layers.Flatten(),
+        tf.keras.layers.Dense(10, activation='softmax')
+    ])
+    model.compile(optimizer='adam', loss='categorical_crossentropy', metrics=['accuracy'])
+    ```
+    This example demonstrates how to use `Conv1D` as part of a Keras Sequential model for processing one-dimensional sequence data.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3694,7 +3808,26 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A 1D transposed convolution layer (also known as deconvolution).
+    This class implements a 1D transposed convolution operation, typically used for upsampling in neural networks. It is particularly useful in tasks such as autoencoders or generative models where increasing the resolution of data is required.
+    Attributes:
+    Methods:
+            - Sets up instance variables and validates `output_padding` against `strides`.
+            - Validates that inputs have rank 3 and that the channel dimension is defined.
+            - Creates kernel and bias weights if applicable.
+            - Computes output dimensions and performs transposed convolution operation.
+            - Adds bias and applies activation function if specified.
+            - Determines the output shape based on input dimensions, kernel size, padding, etc.
+            - Includes all parameters necessary to recreate the layer instance.
+    Usage:
+        - Ideal for upsampling tasks in 1D data such as audio signals or time-series data.
+        - Ensure `output_padding` is less than the corresponding stride value to avoid errors.
+        - Default `data_format='channels_last'`, unless working with a different format.
+    Raises:
+    Example:
+        ```python
+        model = Sequential()
+        model.add(Conv1DTranspose(64, 3, strides=2, padding='same', input_shape=(32, 128)))</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3946,7 +4079,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A 2D convolution layer.
+    The `Conv2D` class implements a two-dimensional convolution operation, which is 
+    fundamental in deep learning models, particularly convolutional neural networks (CNNs). 
+    This class inherits from the `Conv` base class and provides configurations specifically 
+    Attributes:
+              the number of distinct output channels produced by the layer.
+                                    Accepts an integer or a tuple/list of two integers.
+              If a single integer is provided, it implies both dimensions are equal (e.g., `kernel_size=3` means 3x3).
+                                          Defaults to (1, 1).
+              A stride of (2, 2) would mean that the filter jumps two pixels across both dimensions.
+                                 Defaults to 'valid'.
+                                     (default) or `'channels_first'`.
+                                                Defaults to (1, 1).
+                                Defaults to 1.
+                                                 Defaults to None.
+                                                                    Defaults to 'glorot_uniform'.
+                                                                  Defaults to 'zeros'.
+                                                                    Defaults to None.
+                                                                  Defaults to None.
+                                                                     Defaults to None.
+                                                                  Defaults to None.
+                                                                 Defaults to None.
+    Methods:
+    Usage:
+        &gt;&gt;&gt; import tensorflow as tf
+        &gt;&gt;&gt; conv_layer = Conv2D(filters=32, kernel_size=(3, 3), activation='relu')
+        &gt;&gt;&gt; output = conv_layer(input_tensor)
+    Notes:
+        - The input shape should be a 4-dimensional tensor. For `channels_last` data format, 
+          the shape is `(batch, rows, cols, channels)`. For `channels_first`, it's `(batch, channels, rows, cols)`.
+        - This layer supports masking and can be used with TensorFlow's functional API as well as in Sequential models.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -4423,7 +4586,30 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>2D Transposed convolution layer (sometimes called deconvolution).
+    This class implements a transposed version of the standard Conv2D operation,
+    often used in tasks such as upsampling and generative models. It extends 
+    `Conv2D` to support operations that reverse the effect of a forward convolution.
+    Attributes:
+            height and width. Defaults to (1, 1).
+            results in even padding such that output has the same spatial dimensions as input.
+            Used to adjust the shape of the output when strides are greater than one.
+    Raises:
+    Methods:
+        __init__(self, filters, kernel_size, strides=(1, 1), padding='valid', output_padding=None, 
+                 data_format=None, dilation_rate=(1, 1), activation=None, use_bias=True, 
+                 kernel_initializer='glorot_uniform', bias_initializer='zeros', 
+                 kernel_regularizer=None, bias_regularizer=None, activity_regularizer=None, 
+                 kernel_constraint=None, bias_constraint=None, **kwargs):
+            Initializes a Conv2DTranspose layer instance.
+        build(self, input_shape):
+            Creates the layer's weights. Called once from `__call__`.
+        call(self, inputs):
+            Performs the forward pass of data through the layer.
+        compute_output_shape(self, input_shape):
+            Computes the output shape given an input shape.
+        get_config(self):
+            Returns the config of the layer.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -4655,7 +4841,33 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Class Conv3D
+The `Conv3D` class represents a 3-dimensional convolutional layer, extending the functionality 
+of its base class `Conv`. This layer is designed to perform spatial convolutions over each input channel independently,
+making it suitable for processing volumetric data or sequences of images (such as video).
+Attributes:
+                                all dimensions to the same value, or a tuple/list of three integers specifying 
+                                the depth, height, and width of the window.
+                               Defaults to `(1, 1, 1)`, meaning no skipping along any axis.
+                   input so that output size matches the input size. Default is `'valid'`.
+                       the inputs. The default is `None`, which infers from image_data_format convention.
+                                      meaning no dilation.
+                  it implements grouped convolutions.
+                It can be a string identifier or an actual activation layer instance. Default is `None`.
+                        or an initializer object. Default is `'glorot_uniform'`.
+Methods:
+Detailed Sub-Task Docstrings:
+1. Parameters Initialization
+   - This sub-task details how each parameter provided in the constructor (`__init__`) 
+     affects the behavior and configuration of the Conv3D layer, including default values 
+     and expected data types for each argument.
+2. Inheritance and Superclass Call
+   - Describes the relationship between `Conv3D` and its superclass `Conv`. It explains how 
+     `Conv3D` inherits from `Conv`, detailing the role of the `super()` call in initializing 
+     attributes by mapping parameters to those expected by the base class.
+3. Functional Behavior
+   - Explains how an instance of `Conv3D` behaves when integrated into a neural network model, 
+     focusing on the application of 3D convolution during forward passes and any configuration-specific behaviors.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -5149,7 +5361,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>3D Transposed Convolutions (also known as Deconvolutions) layer.
+    This class implements a transposed convolution operation, often used for upsampling in models like autoencoders and GANs. It increases the spatial dimensions of the input volume by applying a deconvolution operation.
+    Attributes:
+    Methods:
+        __init__(self, filters, kernel_size, strides=(1, 1, 1), padding='valid', output_padding=None, data_format=None, dilation_rate=(1, 1, 1), activation=None, use_bias=True, kernel_initializer='glorot_uniform', bias_initializer='zeros', kernel_regularizer=None, bias_regularizer=None, activity_regularizer=None, kernel_constraint=None, bias_constraint=None, **kwargs):
+            Initializes the layer with the specified parameters. Raises a ValueError if `output_padding` is not less than the corresponding stride.
+        build(self, input_shape):
+            Builds the layer by creating weights based on the input shape. Ensures that inputs have rank 5 and that the channel dimension is defined.
+        call(self, inputs):
+            Performs the forward pass for inputs through the layer. Computes the output dimensions and applies the transposed convolution operation.
+        compute_output_shape(self, input_shape):
+            Computes the output shape of the layer given an input shape. Returns a TensorShape representing the expected shape of the output tensor.
+        get_config(self):
+            Returns the config of the layer as a Python dictionary. This can be used to recreate the layer instance with the same configuration.
+    Raises:</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -5295,7 +5521,31 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initialize the Cropping1D layer.
+        Parameters:
+        The `cropping` parameter is normalized using `conv_utils.normalize_tuple` to ensure it has exactly two elements.
+        """
+        super(Cropping1D, self).__init__(**kwargs)
+        """
+        Compute the output shape of the layer given an input shape.
+        Parameters:
+        Returns:
+        - A TensorShape object representing the shape of the output tensor after cropping.
+        This method calculates the new length of the temporal dimension by subtracting the start and end crop values from the original length.
+        """
+        input_shape = tensor_shape.TensorShape(input_shape).as_list()
+            length = input_shape[1] - self.cropping[0] - self.cropping[1]
+        else:
+            length = None
+        """
+        Apply the cropping operation to the input data.
+        Parameters:
+        Returns:
+        - A tensor with the same batch size and number of features, but reduced time steps due to cropping.
+        This method adjusts the temporal dimension according to the specified cropping values, handling cases where no end crop is needed separately for efficiency.
+        """
+        else:</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -5534,7 +5784,50 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Cropping2D Layer
+    This class implements a Cropping2D layer in Keras, which is used for cropping images along 
+    the height and width dimensions. The task of implementing this layer can be divided into 
+    several sub-tasks:
+    1. Initialization:
+       - Define the `__init__` method to set up the cropping parameters.
+       - Accepts `cropping`, which can be an integer or a tuple specifying how much to crop from each dimension.
+       - Normalize the data format and validate the cropping configuration.
+    2. Output Shape Calculation:
+       - Implement the `compute_output_shape` method to determine the shape of the output tensor after cropping.
+       - Adjust the dimensions based on the specified cropping values and the data format 
+         (channels first or last).
+    3. Cropping Operation:
+       - Define the `call` method to perform the actual cropping operation on the input tensor.
+       - Handle different scenarios for symmetric and asymmetric cropping, considering both channels-first 
+         and channels-last data formats.
+    4. Configuration Retrieval:
+       - Implement the `get_config` method to allow serialization of the layer configuration.
+    Parameters:
+                It can be an integer or a tuple of two integers for symmetric cropping,
+                or a tuple of two tuples for asymmetric cropping (e.g., ((top_crop, bottom_crop), 
+                (left_crop, right_crop))). Default is ((0, 0), (0, 0)).
+                   It can be 'channels_first' or 'channels_last'. If None, a default
+                   value will be used based on Keras settings. Default is None.
+    Raises:
+    Attributes:
+                It can be an integer or a tuple of tuples for asymmetric cropping.
+    Usage Example:
+        ```
+        input_tensor = Input(shape=(32, 32, 3))
+        cropped_tensor = Cropping2D(cropping=((4, 4), (4, 4)))(input_tensor)
+        model = Model(inputs=input_tensor, outputs=cropped_tensor)
+        # The model now crops 4 pixels from each side of the input images.
+        ```
+    Methods:
+      the Cropping2D layer with specified parameters.
+        Parameters:
+                       shape, typically corresponding to (batch_size, height, width, channels) for 'channels_last' 
+                       data format, or (batch_size, channels, height, width) for 'channels_first'.
+        Returns:
+        - A TensorShape object that describes the shape of the output tensor after cropping.
+        Raises:
+      and asymmetric cropping for both data formats ('channels_first' and 'channels_last').
+      necessary to recreate the layer instance.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -5900,7 +6193,39 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A custom 3D cropping layer that removes slices from the beginning and end along each spatial dimension.
+    This Keras layer is designed to work with 5-dimensional input tensors, where dimensions typically represent 
+    (batch size, depth, height, width, channels) for 'channels_last' data format or 
+    (batch size, channels, depth, height, width) for 'channels_first' data format. It allows for flexible cropping 
+    configurations across the spatial dimensions.
+    Attributes:
+            It can be specified in one of three ways:
+            which means 'channels_last' is assumed.
+    Methods:
+        __init__(self, cropping=((1, 1), (1, 1), (1, 1)), data_format=None, **kwargs):
+            Initializes the Cropping3D layer.
+            Args:
+                    Accepts a single integer for symmetric cropping across all dimensions, 
+                    a tuple of three integers for symmetric cropping by specific amounts per dimension, 
+                    or a tuple of three tuples specifying (start_crop, end_crop) for each dimension.
+                    which corresponds to 'channels_last'.
+            Raises:
+        compute_output_shape(self, input_shape):
+            Computes the output shape after cropping given an input shape.
+            Args:
+                    Expected to be a 5D shape for this layer.
+            Returns:
+        call(self, inputs):
+            Applies the 3D cropping to the input tensor.
+            Args:
+                    (batch size, depth, height, width, channels) or
+                    (batch size, channels, depth, height, width).
+            Returns:
+        get_config(self):
+            Returns the configuration of the layer as a dictionary.
+            This method is used for serializing the model to JSON format, which can then be saved or loaded.
+            Returns:
+    Raises:</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -6326,7 +6651,28 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Purpose:
+    The `DBSCAN` class implements the Density-Based Spatial Clustering of Applications with Noise (DBSCAN) algorithm. This is a widely used unsupervised machine learning method that clusters closely packed points together and identifies outliers in low-density regions. By leveraging sklearn's BaseEstimator and ClusterMixin classes, this implementation provides a flexible framework for density-based clustering.
+    Functionality:
+      - Additional parameters:
+    Attributes:
+            Indices of core samples.
+            Coordinates of core samples.
+            Cluster labels for each point in the dataset.
+    Example Usage:
+    ```python
+    # Sample data
+    X = [[1, 2], [2, 3], [2, 2], [8, 7], [8, 8], [25, 80]]
+    # Instantiate DBSCAN with default parameters
+    dbscan = DBSCAN()
+    # Fit the model and predict cluster labels
+    labels = dbscan.fit_predict(X)
+    ```
+    Notes:
+    - The choice of `eps` and `min_samples` is crucial for the performance of DBSCAN. These parameters should be chosen based on domain knowledge or through experimentation.
+    - For large datasets, consider using efficient data structures or parallel processing to improve computation time.
+    References:
+    - Ester, M., Hotho, A., &amp; Kriegel, H.-P. (1996). A density-based algorithm for discovering clusters in large spatial databases with noise. In Proceedings of the Second International Conference on Knowledge Discovery and Data Mining (pp. 226-231).</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -6703,7 +7049,45 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initializes the DepthwiseConv2D layer with specified parameters.
+        Args:
+        """
+        super(DepthwiseConv2D, self).__init__(filters=None, kernel_size=kernel_size, strides=strides, padding=padding, data_format=data_format, dilation_rate=dilation_rate, activation=activation, use_bias=use_bias, bias_regularizer=bias_regularizer, activity_regularizer=activity_regularizer, bias_constraint=bias_constraint, **kwargs)
+        """
+        Creates the layer weights. Called once from `__call__` when we know the shapes of inputs and outputs.
+        Args:
+        Raises:
+        """
+        input_shape = tensor_shape.TensorShape(input_shape)
+        channel_axis = self._get_channel_axis()
+            raise ValueError('The channel dimension of the inputs to `DepthwiseConv2D` should be defined. Found `None`.')
+        input_dim = int(input_shape[channel_axis])
+        depthwise_kernel_shape = (self.kernel_size[0], self.kernel_size[1], input_dim, self.depth_multiplier)
+        else:
+        """
+        Performs the forward pass of the layer.
+        Args:
+        Returns:
+        """
+        outputs = backend.depthwise_conv2d(inputs, self.depthwise_kernel, strides=self.strides, padding=self.padding, dilation_rate=self.dilation_rate, data_format=self.data_format)
+            outputs = backend.bias_add(outputs, self.bias, data_format=self.data_format)
+    @tf_utils.shape_type_conversion
+        """
+        Computes the output shape given an input shape.
+        Args:
+        Returns:
+        """
+            rows = input_shape[2]
+            cols = input_shape[3]
+            out_filters = input_shape[1] * self.depth_multiplier
+        elif self.data_format == 'channels_last':
+            rows = input_shape[1]
+            cols = input_shape[2]
+            out_filters = input_shape[3] * self.depth_multiplier
+        rows = conv_utils.conv_output_length(rows, self.kernel_size[0], self.padding, self.strides[0], self.dilation_rate[0])
+        cols = conv_utils.conv_output_length(cols, self.kernel_size[1], self.padding, self.strides[1], self.dilation_rate[1])
+        elif self.data_format == 'channels_last':</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -7034,7 +7418,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Embedding layer that maps positive integer indices (e.g., words) to dense vectors of fixed size.
+    This layer is used for embedding input sequences, typically representing words or tokens in natural language processing tasks. It can load pre-trained embeddings or train new ones as part of a neural network model. The layer creates an embedding matrix where each unique index corresponds to a specific vector representation.
+    Arguments:
+    Input shape:
+    Output shape:
+        - If `input_length` is provided, it will be `(batch_size, input_length[i], output_dim)`, where `i` is the position of `None` in `input_shape`.
+    Raises:
+    Examples:
+        ```python
+        model = Sequential()
+        model.add(Embedding(input_dim=10000, output_dim=128))
+        ```
+    Attributes:</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -8426,7 +8822,114 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>The `Flask` class extends the `App` class to provide a comprehensive web application framework using Flask. 
+    It manages various aspects of application setup and request/response lifecycle management.
+    Attributes:
+    Methods:
+        __init__(self, import_name: str, static_url_path: Optional[str] = None, ..., **kwargs):
+            Initializes the Flask application with essential configurations such as static file handling,
+            template directories, and instance paths. Sets up default configurations for various aspects like
+            debugging, session management, and request handling.
+        get_send_file_max_age(self, filename: str | None) -&gt; int | None:
+            Determines the max age for sending files based on the app's configuration.
+            Parameters:
+            Returns:
+        send_static_file(self, filename: str) -&gt; Response:
+            Serves a static file from the configured static folder.
+            Parameters:
+            Returns:
+        open_resource(self, resource: str, mode: str='rb', encoding: str | None=None) -&gt; IO[AnyStr]:
+            Opens a resource file in read mode with optional encoding.
+            Parameters:
+            Returns:
+        create_jinja_environment(self) -&gt; Environment:
+            Creates a Jinja environment configured for rendering templates within the app.
+            Returns:
+        create_url_adapter(self, request: Request | None) -&gt; MapAdapter | None:
+            Binds URL maps to requests or server configurations to facilitate route matching and handling.
+            Parameters:
+            Returns:
+        raise_routing_exception(self, request: Request) -&gt; NoReturn:
+            Raises routing exceptions based on the app's debug mode and request type.
+            Parameters:
+        update_template_context(self, context: dict[str, t.Any]) -&gt; None:
+            Updates the template context with registered processors.
+            Parameters:
+        make_shell_context(self) -&gt; dict[str, t.Any]:
+            Provides a shell context for debugging purposes.
+            Returns:
+        run(self, host: str | None=None, port: int | None=None, debug: bool | None=None, load_dotenv: bool=True, **options: t.Any) -&gt; None:
+            Runs the Flask application on a specified host and port with optional configurations.
+            Parameters:
+        test_client(self, use_cookies: bool=True, **kwargs: t.Any) -&gt; FlaskClient:
+            Creates a test client for testing the Flask app.
+            Parameters:
+            Returns:
+        handle_http_exception(self, e: HTTPException) -&gt; HTTPException | ResponseReturnValue:
+            Handles HTTP exceptions with registered error handlers.
+            Parameters:
+            Returns:
+        handle_user_exception(self, e: Exception) -&gt; HTTPException | ResponseReturnValue:
+            Handles user-defined exceptions and propagates them if necessary.
+            Parameters:
+            Returns:
+        handle_exception(self, e: Exception) -&gt; Response:
+            Handles uncaught exceptions during request processing.
+            Parameters:
+            Returns:
+        log_exception(self, exc_info: tuple[type, BaseException, TracebackType]) -&gt; None:
+            Logs exception details for debugging purposes.
+            Parameters:
+        dispatch_request(self) -&gt; ResponseReturnValue:
+            Dispatches the current request to the appropriate view function.
+            Returns:
+        full_dispatch_request(self) -&gt; Response:
+            Handles a complete request cycle including preprocessing, dispatching, and finalizing responses.
+            Returns:
+        finalize_request(self, rv: ResponseReturnValue | HTTPException, from_error_handler: bool=False) -&gt; Response:
+            Finalizes the response after processing or error handling.
+            Parameters:
+            Returns:
+        make_default_options_response(self) -&gt; Response:
+            Creates a default OPTIONS response with allowed methods.
+            Returns:
+        ensure_sync(self, func: Callable[..., Any]) -&gt; Callable[..., Any]:
+            Ensures that a function is executed synchronously if it's asynchronous.
+            Parameters:
+            Returns:
+        async_to_sync(self, func: Callable[..., Coroutine[Any, Any, Any]]) -&gt; Callable[..., Any]:
+            Converts an asynchronous function to a synchronous one using `asgiref`.
+            Parameters:
+            Returns:
+        url_for(self, endpoint: str, **values) -&gt; str:
+            Generates a URL for the given endpoint with optional parameters.
+            Parameters:
+            Returns:
+        make_response(self, rv: ResponseReturnValue) -&gt; Response:
+            Creates an HTTP response from various return types of view functions.
+            Parameters:
+            Returns:
+        preprocess_request(self) -&gt; ft.ResponseReturnValue | None:
+            Runs pre-request processing functions.
+            Returns:
+        process_response(self, response: Response) -&gt; Response:
+            Processes the HTTP response after request handling with post-response functions.
+            Parameters:
+            Returns:
+        do_teardown_request(self, exc: BaseException | None=_sentinel) -&gt; None:
+            Tears down resources after a request is processed.
+            Parameters:
+        do_teardown_appcontext(self, exc: BaseException | None=_sentinel) -&gt; None:
+            Tears down app context resources after processing.
+            Parameters:
+        wsgi_app(self, environ: WSGIEnvironment, start_response: StartResponse) -&gt; Iterable[bytes]:
+            The main entry point for handling requests in the WSGI environment.
+            Parameters:
+            Returns:
+        __call__(self, environ: WSGIEnvironment, start_response: StartResponse) -&gt; Iterable[bytes]:
+            Invokes the WSGI application with the given environment and response starter.
+            Parameters:
+            Returns:</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -8960,7 +9463,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A transformer that applies a user-defined function to each element of an input array.
+    This class allows users to apply arbitrary functions (and their inverses) to data,
+    providing flexibility in feature engineering and transformation tasks. It supports
+    validation checks and custom feature names for output columns.
+    Parameters
+    ----------
+        The function to use for transforming the data. If None, no transformation is applied.
+        The function to use for inverting the transform. Must be a strict inverse of `func`.
+        Whether to validate input parameters and output shapes. Validation can ensure that
+        transformations are correctly applied but may slow down processing.
+        Whether to allow sparse matrix inputs. If False, sparse matrices will be converted
+        to dense format before transformation.
+        Whether to verify that `func` and `inverse_func` are strict inverses of each other.
+        This is done by applying both functions in sequence to a subset of the data.
+        Defines the output feature names. Can be 'one-to-one' for direct mapping from input,
+        a callable that generates new names, or a predefined list/set of names.
+        Additional keyword arguments to pass to `func` during transformation.
+        Additional keyword arguments to pass to `inverse_func` during inverse transformation.
+    Attributes
+    ----------
+        Number of features in the input data as determined by the `fit` method.
+        Names of features seen during `fit`.
+    Methods
+    -------
+    fit(X, y=None):
+        Learns the number of features and checks inverse functions if applicable.
+    transform(X):
+        Applies the transformation function to input data `X`.
+    inverse_transform(X):
+        Applies the inverse transformation function to data `X`.
+    get_feature_names_out(input_features=None):
+        Returns output feature names based on the configuration.
+    set_output(*, transform=None):
+        Configures the desired output format for transformed data.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -9538,7 +10074,57 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Class GaussianMixture(BaseMixture)
+----------------------------------
+The `GaussianMixture` class implements a Gaussian Mixture Model (GMM), which is a probabilistic model 
+that assumes all data points are generated from a mixture of several Gaussian distributions with unknown 
+parameters. It extends the `BaseMixture` class and employs the Expectation-Maximization (EM) algorithm 
+Attributes:
+  The number of mixture components.
+  Specifies the type of covariance parameters ('full', 'tied', 'diag', or 'spherical').
+  Convergence threshold for the EM algorithm.
+  Regularization added to the diagonal of covariance matrices to ensure positive definiteness.
+  Maximum number of iterations in the EM algorithm.
+  Number of initializations to perform. The best results are kept.
+  Method for initialization ('kmeans' or 'random').
+  Initial values for the mixture component weights, means, and precision matrices.
+  Controls randomness in parameter initialization.
+  If True, reuse the previous solution as initialization; otherwise, reinitialize.
+  Verbosity level of progress messages during EM iterations.
+  Interval for printing progress messages.
+Methods:
+- __init__(self, n_components=1, *, covariance_type='full', tol=0.001, reg_covar=1e-06, max_iter=100, 
+           n_init=1, init_params='kmeans', weights_init=None, means_init=None, precisions_init=None, 
+           random_state=None, warm_start=False, verbose=0, verbose_interval=10)
+  Initializes the GaussianMixture object with specified parameters.
+- _check_parameters(self, X)
+  Validates initial parameter values based on input data shape. Ensures `weights_init`, `means_init`, 
+  and `precisions_init` are compatible with the number of components and features in `X`.
+- _initialize_parameters(self, X, random_state)
+  Initializes model parameters either using provided values or by computing them from the data `X`. 
+  If necessary, it calls the superclass method to perform initialization.
+- _initialize(self, X, resp)
+  Sets initial values for weights, means, and covariances. Uses responsibility matrix `resp` if available; 
+  otherwise, estimates parameters based on input data `X`.
+- _m_step(self, X, log_resp)
+  Performs the M-step of the EM algorithm by updating model parameters (`weights_`, `means_`, `covariances_`) 
+  using current responsibilities.
+- _estimate_log_prob(self, X)
+  Computes the logarithm of the probability density function for each sample in `X` under the current model parameters.
+- _estimate_log_weights(self)
+  Returns the logarithm of the mixture component weights.
+- _compute_lower_bound(self, _, log_prob_norm)
+  Calculates the lower bound of the log likelihood during optimization. This method is typically used internally 
+  by the EM algorithm to monitor convergence.
+- _get_parameters(self)
+- _set_parameters(self, params)
+  Sets the model parameters from a given tuple `params`. Updates internal attributes based on specified covariance type.
+- _n_parameters(self)
+  Computes the total number of free parameters in the model based on its configuration (`covariance_type`).
+- bic(self, X)
+  Calculates the Bayesian Information Criterion (BIC) for the current model fitted to data `X`.
+- aic(self, X)
+  Computes the Akaike Information Criterion (AIC) for the current model fitted to data `X`.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -9694,7 +10280,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>GlobalAveragePooling1D Class
+    This class implements the Global Average Pooling operation for 1D input data. 
+    It is a subclass of `GlobalPooling1D` and provides functionality to pool over 
+    the entire spatial dimension of each feature map, reducing each map to a single 
+    number by taking its average.
+    Attributes:
+    Methods:
+        __init__(self, data_format='channels_last', **kwargs):
+            Initializes the GlobalAveragePooling1D instance with optional parameters.
+            Parameters:
+                                   Options are 'channels_first' or 'channels_last'.
+        call(self, inputs, mask=None):
+            Performs the global average pooling operation on the input tensor.
+            Parameters:
+                                 `data_format='channels_last'`, or `(batch_size, channels, steps)` 
+                                         dimensions of `inputs` that specifies which timesteps should be masked.
+            Returns:
+                A tensor with global average pooling applied. The output shape will be `(batch_size, channels)` if 
+                `keepdims=False`, or `(batch_size, 1, channels)` if `keepdims=True`.
+        compute_mask(self, inputs, mask=None):
+            Computes the mask for the layer's input.
+            Parameters:
+            Returns:</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -9817,7 +10425,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>GlobalAveragePooling2D Class
+Purpose:
+- The `GlobalAveragePooling2D` class is designed to perform global average pooling on a given input tensor. This operation reduces the spatial dimensions (height and width) of an input feature map by computing their mean, effectively converting each channel's 2D features into a single value.
+- It extends from the base class `GlobalPooling2D`, inheriting its properties and functionalities while providing a specific implementation for average pooling.
+Methods:
+Parameters and Attributes:
+Return Values:
+- The method returns a tensor where spatial dimensions (height and width) are averaged out for each channel. This results in either a vector of average values per batch or a reduced tensor based on `keepdims`.
+- For 'channels_last', reduction occurs over axes [1, 2] (i.e., height and width). For 'channels_first', it reduces over axes [2, 3]. The shape of the returned tensor is influenced by the value of `keepdims`, potentially retaining reduced dimensions as singletons.
+Exceptions:
+- No specific exceptions are handled within this method. However, incorrect data format specifications or incompatible input shapes may lead to runtime errors from underlying backend operations.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -9932,7 +10550,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Performs global average pooling operation for 3D input data.
+    Inherits from `GlobalPooling3D`.
+    This class implements a layer that performs global average pooling over the spatial dimensions (depth, height, width) of 
+    3D inputs. The purpose is to reduce each feature map to a single number by averaging all values in it, effectively reducing
+    the dimensions while retaining the batch size and channels. This operation is commonly used in convolutional neural networks
+    to transition from spatial feature maps to fully connected layers.
+    Attributes:
+              Input shape should be `(batch_size, depth, height, width, channels)`.
+              Input shape should be `(batch_size, channels, depth, height, width)`.
+                         Default is `False`. If set to `True`, the output will have an added singleton dimension(s).
+    Methods:
+        call(inputs):
+            Applies global average pooling to the input data.
+            Args:
+                    `(batch_size, depth, height, width, channels)` if 
+                    `data_format` is 'channels_last', or 
+                    `(batch_size, channels, depth, height, width)` if 
+                    `data_format` is 'channels_first'.
+            Returns:
+                        The shape will be reduced to `(batch_size, channels)` 
+    Notes:
+        - This implementation relies on the backend's mean function for calculating averages.
+        - Supported backends include TensorFlow and PyTorch. Ensure compatibility by checking the backend configuration.
+        - If inputs do not match expected dimensions or formats, errors may be raised; handle these appropriately in your code.
+    Example Usage:
+        # Assuming data_format='channels_last'
+        layer = GlobalAveragePooling3D(data_format='channels_last', keepdims=False)
+        output = layer.call(input_tensor)
+        # Assuming data_format='channels_first'
+        layer = GlobalAveragePooling3D(data_format='channels_first', keepdims=True)
+        output = layer.call(input_tensor)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -10067,7 +10715,54 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A class that implements global max pooling over the temporal dimension of a sequence.
+    This class inherits from `GlobalPooling1D` and provides functionality to perform 
+    global max pooling on 1-dimensional inputs. It is designed for use in neural network
+    architectures where it's necessary to reduce the input size by taking the maximum value 
+    across each feature map (or channel) of a sequence.
+    Attributes:
+    -----------
+        The format of the input data, either 'channels_last' or 'channels_first'.
+        Whether to retain the reduced axis as dimension with size 1 in the output tensor.
+    Methods:
+    --------
+    call(inputs):
+        Applies global max pooling over the temporal dimension of the input tensor.
+    """
+        """
+        Apply global max pooling to the input tensor along the specified axis.
+        Parameters:
+        -----------
+            A 3D tensor with shape (batch_size, steps, features) if `data_format` is 
+            'channels_last', or (batch_size, features, steps) if `data_format` is 
+            'channels_first'. This represents the input data on which global max pooling 
+            will be performed.
+        Returns:
+        --------
+        Tensor
+            A tensor with shape (batch_size, features) if `keepdims` is False. If `keepdims`
+            is True, the output shape will include a dimension of size 1 for the pooled axis,
+            resulting in either (batch_size, 1, features) or (batch_size, features, 1), 
+            depending on the `data_format`.
+        Raises:
+        -------
+        ValueError
+            If `inputs` does not have a rank of 3.
+        Examples:
+        ---------
+        &gt;&gt;&gt; # Assuming self.data_format='channels_last' and keepdims=False
+        &gt;&gt;&gt; import numpy as np
+        &gt;&gt;&gt; from keras.layers import Input
+        &gt;&gt;&gt; global_max_pooling_1d = GlobalMaxPooling1D()
+        &gt;&gt;&gt; outputs = global_max_pooling_1d.call(inputs)
+        Details:
+        --------
+        The method determines which axis corresponds to the temporal steps based on the 
+        `data_format` attribute. For 'channels_last', it pools across the second dimension 
+        (axis=1). For 'channels_first', pooling is done over the third dimension (axis=2).
+        It uses Keras backend's max function to perform the reduction operation, retaining
+        only the maximum value for each feature map or channel. The `keepdims` parameter 
+        controls whether the reduced axis is retained with size 1 in the output tensor.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -10190,7 +10885,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>The `GlobalMaxPooling2D` class is a specialized layer used primarily in neural network models 
+    that involve convolutional layers. It extends the base `GlobalPooling2D` class and implements 
+    global max pooling over 2D spatial data, such as feature maps. This operation reduces each channel 
+    of the input to its maximum value, effectively summarizing spatial information into a single scalar 
+    per channel. By doing so, it helps in reducing the dimensionality of the input while retaining important 
+    features.
+    Method Description:
+      It accepts an input tensor and applies global max pooling according to the specified data format (`channels_last`
+      or `channels_first`). The method utilizes the backend's `max` function, where the axis parameter 
+      depends on the `data_format`. For 'channels_last', it pools over the spatial dimensions [1, 2], while for 'channels_first',
+      it uses [2, 3]. This results in a tensor with reduced dimensions, retaining only the maximum values across specified axes.
+    Parameters and Return Values:
+      either be 'channels_last' (default), where channels are the last dimension, or 'channels_first', 
+      where channels come first.
+      dimensions in the output tensor.
+      reduced dimensions are retained as singletons; otherwise, they are removed from the output shape.
+    This class provides an efficient mechanism for reducing spatial dimensions while preserving essential 
+    features for subsequent layers in a neural network model.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -10305,7 +11017,50 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>GlobalMaxPooling3D performs a global max pooling operation on an input tensor.
+    This class extends `GlobalPooling3D` by implementing the maximum reduction 
+    across specified axes for 3-dimensional inputs. It reduces each feature map in 
+    the input tensor to its maximum value, summarizing spatial dimensions into a 
+    single scalar per feature map.
+    Methods
+    -------
+    call(self, inputs):
+        Executes the global max pooling operation on the given 3D input tensor.
+    Attributes
+    ----------
+        The ordering of the dimensions in the inputs. Commonly 'channels_last' or 'channels_first'.
+        Whether to retain reduced dimensions with size 1 in the output shape.
+    call(self, inputs)
+        Execute global max pooling operation on a 3D input tensor.
+    Parameters
+    ----------
+        A 5-dimensional tensor. Its shape is:
+        - `(batch_size, depth, height, width, channels)` for 'channels_last' data format,
+        - or `(batch_size, channels, depth, height, width)` for other formats (typically 'channels_first').
+    Returns
+    -------
+    tensor
+        A tensor containing the maximum values from each input feature map. The output shape 
+        depends on `keepdims`:
+        - If `keepdims` is True, retains reduced dimensions with size 1.
+        - Otherwise, these dimensions are removed.
+    Raises
+    ------
+    ValueError
+        If the input tensor does not have 5 dimensions or if an unsupported data format is used.
+    Data Format Handling
+    --------------------
+    The method handles two primary data formats:
+    Keepdims Option
+    ---------------
+    The `keepdims` parameter determines whether reduced dimensions are retained with a size of 
+    1 in the output tensor (`True`) or removed (`False`). This affects the number of dimensions 
+    in the output, which can be important for subsequent operations expecting specific input shapes.
+    Dependencies
+    ------------
+    This method relies on a backend library, referred to as `backend`, which provides the max operation.
+    The exact implementation details of this backend may vary (e.g., TensorFlow, PyTorch) and are 
+    responsible for executing tensor manipulation and pooling operations efficiently.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -10405,7 +11160,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>GlobalPooling1D Layer
+This class implements a global pooling layer for 1-dimensional input data. It reduces spatial dimensions (i.e., length) of an input tensor, retaining only the most significant features along the specified axis.
+Attributes:
+Methods:
+Constructor Parameters:
+Input Specification:
+Methods:
+compute_output_shape(input_shape):
+    Computes the output shape of the layer based on the input shape. The method considers the `data_format` and `keepdims` parameters to determine how dimensions are reduced.
+    Parameters:
+    Returns:
+        A TensorShape object representing the calculated output shape.
+    Behavior:
+    - If `data_format` is 'channels_first':
+        - With `keepdims=True`, returns a shape with dimensions [batch_size, channels, 1].
+        - With `keepdims=False`, returns a shape with dimensions [batch_size, channels].
+    - If `data_format` is 'channels_last':
+        - With `keepdims=True`, returns a shape with dimensions [batch_size, 1, length].
+        - With `keepdims=False`, returns a shape with dimensions [batch_size, length].
+call(inputs):
+    Raises NotImplementedError. This method should be implemented by subclasses to define the actual pooling operation.
+get_config():
+    Serializes the layer's configuration into a dictionary for saving and loading purposes.
+    Returns:
+Dependencies:
+Example Usage:
+    # Instantiate GlobalPooling1D layer with 'channels_last' and keepdims=True
+    global_pooling_layer = GlobalPooling1D(data_format='channels_last', keepdims=True)
+    # Define a model using the GlobalPooling1D layer
+    input_tensor = Input(shape=(None, 64))
+    pooled_output = global_pooling_layer(input_tensor)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -10507,7 +11292,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Abstract base class for global pooling layers in Keras. This class provides a framework 
+    (height and width) to 1 by applying a specific pooling operation across these dimensions.
+        - The `GlobalPooling2D` class is an abstract base class designed for creating layers 
+          that perform global pooling on 4D input tensors.
+        - It serves as a template, defining the necessary structure and methods required to implement 
+          different types of global pooling operations (e.g., Global Average Pooling, Global Max Pooling).
+        - The key functionality revolves around abstracting the pooling process over spatial dimensions.
+        __init__(self, data_format=None, keepdims=False, **kwargs)
+            Initializes the `GlobalPooling2D` layer with specified configurations.
+            Parameters:
+                                   Common values are 'channels_last' and 'channels_first'.
+        compute_output_shape(self, input_shape)
+            Computes the output shape of the layer given an input shape.
+            Parameters:
+            Returns:
+                A `TensorShape` object representing the shape of the output tensor after pooling.
+        call(self, inputs)
+            Abstract method that should be implemented by subclasses to define the specific pooling operation.
+            Parameters:
+            Raises:
+        get_config(self)
+            Returns the configuration of the layer as a dictionary, which can be used
+            Returns:
+                A dictionary containing the layer's configuration parameters such as `data_format` 
+                and `keepdims`.
+        - To use this class, create a subclass that implements the `call` method with specific pooling logic.
+        Example of subclassing for Global Average Pooling:
+          ```python
+          # Example usage in a Keras model
+          model = Sequential([
+              Conv2D(32, (3, 3), activation='relu', input_shape=(28, 28, 1)),
+              GlobalAveragePooling2D()
+          ])
+          ```
+        - This structure allows for flexible implementation of different global pooling strategies by 
+          subclassing `GlobalPooling2D` and providing the specific logic in the `call` method.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -10607,7 +11427,35 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initializes the GlobalPooling3D layer with specified parameters.
+        Args:
+                Can be 'channels_last' or 'channels_first'. Defaults to None.
+        Raises:
+        This method sets up the layer's configuration, normalizes the data format,
+        and specifies that inputs must be 5-dimensional.
+        """
+        super(GlobalPooling3D, self).__init__(**kwargs)
+        """
+        Computes the shape of the output tensor based on the input shape and layer configurations.
+        Args:
+                Must be 5-dimensional as specified by `input_spec`.
+        Returns:
+        This method calculates the output shape considering whether channels are last or first
+        in the input and whether reduced dimensions should be kept with size 1.
+        """
+        input_shape = tensor_shape.TensorShape(input_shape).as_list()
+            else:
+        elif self.keepdims:
+        else:
+        """
+        Placeholder method to be implemented for specific global pooling logic.
+        Args:
+        Raises:
+        This method is intended to be overridden in subclasses where users define their
+        custom global pooling logic.
+        """
+        raise NotImplementedError</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -10931,7 +11779,59 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initialize the GroupTimeSeriesSplit with specified parameters.
+        Parameters
+        ----------
+            The number of samples in the test set.
+            The number of samples in the training set. If not provided, it will be 
+            calculated based on `n_splits`.
+            The total number of splits (folds). Required if `train_size` is not specified.
+            The number of samples to skip between the end of the training set and 
+            the start of the test set.
+            The number of groups to move forward for the next split.
+            The type of window to use. 'rolling' uses a fixed-size training set, while 
+            'expanding' increases the size of the training set with each split.
+        Raises
+        ------
+        ValueError
+            If neither `train_size` nor `n_splits` is defined.
+            If `window_type` is not 'rolling' or 'expanding'.
+            If `train_size` is specified with an expanding window type.
+        """
+            raise ValueError('Either train_size or n_splits should be defined')
+            raise ValueError('Window type can be either "rolling" or "expanding"')
+            raise ValueError('Train size can be specified only with rolling window')
+        """
+        Generate indices to split data into training and testing sets.
+        Parameters
+        ----------
+            Training data, where `n_samples` is the number of samples 
+            and `n_features` is the number of features.
+            The target variable for supervised learning problems.
+            Group labels for the samples used while splitting the dataset into 
+            train/test set.
+        Yields
+        ------
+            The training and testing indices to split data in train/test sets.
+        Raises
+        ------
+        ValueError
+            If `groups` is not specified or if groups are non-consecutive.
+        """
+        # Implementation details...
+        """
+        Get the number of splitting iterations in the cross-validator.
+        Parameters
+        ----------
+            Always ignored, exists for compatibility.
+            Always ignored, exists for compatibility.
+            Group labels for the samples used while splitting the dataset into 
+            train/test set. Ignored.
+        Returns
+        -------
+            Number of re-shuffling &amp; splitting iterations in the cross-validator.
+        """</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -11156,7 +12056,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>_BaseModel.__init__(self)
+        _Cluster.__init__(self)
+        _IterativeModel.__init__(self)
+        """
+        Fits the K-means model to the input data `X`.
+        Parameters:
+        Returns:
+        """
+        n_samples = X.shape[0]
+            rgen = np.random.RandomState(self.random_seed)
+            idx = rgen.choice(n_samples, self.k, replace=False)
+            new_centroids = np.array([np.mean(X[self.clusters_[k]], axis=0) for k in sorted(self.clusters_.keys())])
+                break
+            else:
+        """
+        Calculates and yields the index of the nearest centroid for each sample in `X`.
+        Parameters:
+        Yields:
+        """
+            dist = np.sqrt(np.sum(np.square(sample - self.centroids_), axis=1))
+            yield np.argmin(dist)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -11522,7 +12442,100 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initialize the LabelBinarizer with specified parameters.
+        Parameters
+        ----------
+            The value to use for negative labels.
+            The value to use for positive labels. Must be strictly greater than `neg_label`.
+            If True, the output will be a sparse matrix. This is useful when dealing
+        Raises
+        ------
+        ValueError
+            If `neg_label` is not strictly less than `pos_label`, or if conditions 
+            negative labels).
+        Notes
+        -----
+        - Sparse output is only supported when `pos_label` is non-zero and 
+          `neg_label` is zero.
+        - The default configuration sets up a typical binary transformation with 
+          positive labels as 1 and negative labels as 0, producing dense output.
+        Examples
+        --------
+        &gt;&gt;&gt; lb = LabelBinarizer(neg_label=0, pos_label=1)
+        &gt;&gt;&gt; lb.neg_label
+        0
+        &gt;&gt;&gt; lb_sparse = LabelBinarizer(sparse_output=True)
+        &gt;&gt;&gt; lb_sparse.sparse_output
+        True
+        """
+    @_fit_context(prefer_skip_nested_validation=True)
+        """
+        Learn the classes and verify that they are consistent with `neg_label` 
+        and `pos_label`.
+        Parameters
+        ----------
+            Target values.
+        Returns
+        -------
+            Fitted instance of LabelBinarizer.
+        Raises
+        ------
+        ValueError
+            If `neg_label` is not strictly less than `pos_label`, or if conditions 
+            If `y` contains multioutput target data, or if it has 0 samples.
+        """
+            raise ValueError(f'neg_label={self.neg_label} must be strictly less than pos_label={self.pos_label}.')
+            raise ValueError(f'Sparse binarization is only supported with non zero pos_label and zero neg_label, got pos_label={self.pos_label} and neg_label={self.neg_label}')
+            raise ValueError('Multioutput target data is not supported with label binarization')
+        """
+        Fit to data and transform it into binary format.
+        Parameters
+        ----------
+            Target values.
+        Returns
+        -------
+            Transformed target values.
+        """
+        """
+        Transform target values to binary format using learned classes.
+        Parameters
+        ----------
+            Target values.
+        Returns
+        -------
+            Transformed target values.
+        Raises
+        ------
+        ValueError
+            If the object was not fitted with multilabel input but `y` is multilabel.
+        """
+        check_is_fitted(self)
+        y_is_multilabel = type_of_target(y).startswith('multilabel')
+            raise ValueError('The object was not fitted with multilabel input.')
+        """
+        Convert binary matrix back into original label representation.
+        Parameters
+        ----------
+            Binary target values.
+            Threshold to use for inverse transformation. If None, the default 
+            value is used.
+        Returns
+        -------
+            Inverse transformed target values.
+        Raises
+        ------
+        ValueError
+            If `Y` has an invalid shape or type.
+        """
+        check_is_fitted(self)
+            threshold = (self.pos_label + self.neg_label) / 2.0
+            y_inv = _inverse_binarize_multiclass(Y, self.classes_)
+        else:
+            y_inv = _inverse_binarize_thresholding(Y, self.y_type_, self.classes_, threshold)
+            y_inv = sp.csr_matrix(y_inv)
+        elif sp.issparse(y_inv):
+            y_inv = y_inv.toarray()</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -11750,7 +12763,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A class for encoding categorical labels into integer values ranging from 0 to n_classes-1.
+    This transformer is designed to convert non-numerical labels (as long as they are hashable) 
+    into numerical labels. It facilitates the use of categorical data in machine learning algorithms, 
+    which typically require numerical inputs. The `LabelEncoder` can be employed for both classification 
+    and regression tasks where label encoding is necessary.
+    Methods
+    -------
+    fit(y)
+        Learn the unique classes from y and store them as an attribute.
+    fit_transform(y)
+        Fit the encoder on the data and simultaneously transform it to encoded labels.
+    transform(y)
+        Transform non-numerical labels to their corresponding integer encodings using a pre-fitted model.
+    inverse_transform(y)
+        Convert previously encoded labels back to their original string or categorical representation.
+    _more_tags()
+        Provide additional compatibility tags for integration with other components in the machine learning pipeline.
+    Parameters
+    ----------
+        If specified keys are present in the input, automatically wraps the output as a dictionary. 
+        This is useful when integrating with pipelines that expect certain output formats.
+    Attributes
+    ----------
+        Contains the unique class labels discovered during fitting.
+    Notes
+    -----
+    - The `LabelEncoder` should be used only on target variables or features where encoding to integers 
+      makes sense (e.g., categorical data).
+    - For multi-dimensional input, ensure that it is converted into a one-dimensional array before using this encoder.
+    Examples
+    --------
+    &gt;&gt;&gt; from sklearn.preprocessing import LabelEncoder
+    &gt;&gt;&gt; le = LabelEncoder()
+    &gt;&gt;&gt; labels = ['cat', 'dog', 'fish', 'cat']
+    &gt;&gt;&gt; encoded_labels = le.fit_transform(labels)
+    &gt;&gt;&gt; original_labels = le.inverse_transform(encoded_labels)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -12061,7 +13109,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Linear Regression Model
+    The `LinearRegression` class implements linear regression using various methods: 
+    'SGD' (Stochastic Gradient Descent), 'direct', 'QR decomposition', and 'SVD' (Singular Value Decomposition). 
+    This model is built by inheriting from `_BaseModel`, `_IterativeModel`, and `_Regressor`.
+    Attributes
+    ----------
+        The method to use for fitting the model. Supported methods are:
+        The learning rate for the optimization algorithm when using 'SGD'.
+        Number of iterations over the training data when using 'SGD'.
+        Size of minibatches to be used if 'sgd' method is chosen. If not using 'sgd', set this to `None`.
+        Seed for random number generator to ensure reproducibility.
+        Frequency of progress printing during training. If 0, no output will be printed.
+        Indicates whether the model has been fitted.
+        Intercept term learned by the model.
+        Weight vector learned by the model.
+        List to store cost values during training for each epoch (if using 'sgd').
+    Methods
+    -------
+    __init__(self, method='direct', eta=0.01, epochs=50, minibatches=None, random_seed=None, print_progress=0)
+        Initializes a new instance of `LinearRegression` with the specified parameters.
+        Parameters:
+        Raises:
+    _fit(self, X, y, init_params=True)
+        Fits the model to the training data `X` and target values `y`.
+        Parameters:
+        Returns:
+    _normal_equation(self, X, y)
+        Solves for the optimal weights using the normal equation method.
+        Parameters:
+        Returns:
+    _net_input(self, X)
+        Computes the net input (predictions) given input features `X`.
+        Parameters:
+        Returns:
+    _predict(self, X)
+        Predicts target values for the provided input features `X`.
+        Parameters:
+        Returns:
+    _sum_squared_error_cost(self, y, y_val)
+        Calculates the sum of squared errors cost between actual and predicted target values.
+        Parameters:
+        Returns:
+    Notes
+    -----
+    - If `method` is not 'sgd', ensure that `minibatches` is set to `None`.
+    - The class raises a ValueError if an unsupported method is provided or if `minibatches` is not None when `method` is not 'sgd'.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -12346,7 +13439,58 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A logistic regression model that implements binary classification using a 
+    sigmoid activation function and supports L2 regularization. This class is 
+    designed to be initialized with specific hyperparameters and fitted on provided data.
+    Attributes:
+            Determines the step size at each iteration while moving toward a minimum of the loss function.
+            Specifies how many times the learning algorithm will pass through the entire training dataset.
+            If set to 0, no L2 regularization is applied. Helps prevent overfitting by adding penalty on large weights.
+            If set to 1, full batch gradient descent is used. Allows for faster convergence and better generalization.
+            If None, the random state will be unpredictable. Ensures consistent results across runs when specified.
+            Useful for monitoring the model's learning process and debugging.
+    Methods:
+        __init__(self, eta=0.01, epochs=50, l2_lambda=0.0, minibatches=1, random_seed=None, print_progress=False):
+            Initializes the logistic regression model with specified hyperparameters.
+            Sets up necessary attributes for training the model.
+        _forward(self, X):
+            Computes the forward pass by applying the sigmoid activation function 
+            to the linear combination of inputs and weights. Returns predicted probabilities.
+        _backward(self, X, y_true, y_probas):
+            Computes gradients of the loss with respect to the network's weights 
+            and bias using backpropagation. Essential for updating model parameters during training.
+        _fit(self, X, y, init_params=True):
+            Fits the model to the training data by performing gradient descent 
+            over a specified number of epochs. Optionally initializes parameters if required.
+            Updates internal state to reflect trained model status.
+        _predict(self, X):
+            Predicts binary labels for input samples based on learned weights and bias.
+            Returns 0 or 1 predictions for each sample in X.
+        _net_input(self, X):
+            Computes the linear combination of inputs and weights plus the bias term.
+            Used internally to calculate model predictions before applying activation function.
+        predict_proba(self, X):
+            Returns probability estimates for the target classes as predicted by 
+            the model. Provides the likelihood of samples belonging to class 1.
+        _logit_cost(self, y, y_val):
+            Calculates the log-likelihood cost with optional L2 regularization.
+            Measures how well the model's predictions match the actual labels.
+        _sigmoid_activation(self, z):
+            Applies the sigmoid function to input data `z`.
+            Transforms linear outputs into probabilities between 0 and 1.
+    Notes:
+        - Ensure that the input features are scaled appropriately for optimal performance.
+        - The method `_fit` modifies internal state variables (`self.w_`, `self.b_`, `self.cost_`) which reflect 
+          the trained model parameters and cost history.
+        - Regularization is controlled by `l2_lambda`. A higher value will increase the penalty on weights, potentially 
+          leading to underfitting if too large.
+        - Be cautious of overfitting, especially with a high number of epochs or insufficient data; cross-validation can help mitigate this risk.
+        - The random seed (`random_seed`) is crucial for reproducibility when shuffling data during mini-batch creation.
+    Example Usage:
+        &gt;&gt;&gt; model = LogisticRegression(eta=0.01, epochs=100, l2_lambda=0.1)
+        &gt;&gt;&gt; model._fit(X_train, y_train)
+        &gt;&gt;&gt; predictions = model._predict(X_test)
+        &gt;&gt;&gt; probabilities = model.predict_proba(X_test)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -12534,7 +13678,30 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A base class for defining custom loss functions in Keras.
+This abstract class serves as a template to create new loss functions by implementing the `call` method. 
+It facilitates standard operations such as tensor conversion, masking, and reduction of loss values.
+Attributes:
+                     Default is 'sum_over_batch_size'.
+Methods:
+    __init__(self, name=None, reduction='sum_over_batch_size', dtype=None):
+    @property
+        Returns the computed data type based on the dtype policy.
+    __call__(self, y_true, y_pred, sample_weight=None):
+        Computes the loss between true labels (`y_true`) and predictions (`y_pred`). 
+        Applies masks if available and reduces losses according to the specified reduction method.
+        Parameters:
+    call(self, y_true, y_pred):
+        Abstract method that must be implemented by subclasses. 
+        Defines the specific computation of the loss between `y_true` and `y_pred`.
+    get_config(self):
+        Returns a dictionary containing configuration parameters of the loss function.
+        Useful for serializing the object state.
+    @classmethod
+        Creates an instance of the Loss class using its configuration dictionary.
+    _obj_type(self):
+        Returns a string representation of the object type, which is 'Loss'.
+Raises:</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -12704,7 +13871,16 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>The `MaxPooling1D` class is a specific implementation of the `Pooling1D` layer that performs max pooling operation on 1-dimensional temporal data. It is commonly used in convolutional neural networks to down-sample input data by reducing its dimensionality while preserving important features.
+    This class inherits from `Pooling1D` and utilizes a backend function `pool2d` with `pool_mode='max'` for the max pooling operation.
+    Attributes:
+    Methods:
+        - __init__(self, pool_size=2, strides=None, padding='valid', data_format='channels_last', **kwargs):
+            Initializes a MaxPooling1D layer with specified parameters.
+    Constructor for the MaxPooling1D Layer:
+    This constructor initializes a MaxPooling1D layer that performs max pooling operation on 1-dimensional temporal data. It is designed to down-sample input by reducing its dimensionality while preserving essential features through the max pooling mechanism.
+    Parameters:
+    The MaxPooling1D layer is particularly useful in convolutional neural networks for feature extraction by focusing on dominant patterns in temporal data.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -12956,7 +14132,46 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>The `MaxPooling2D` class implements a max pooling operation over 2D spatial data,
+    which is commonly used in convolutional neural networks (CNNs) to downsample 
+    input features. This layer inherits from the `Pooling2D` base class, adapting
+    its functionality specifically for performing max pooling.
+    Parameters:
+    ----------
+        A tuple specifying the height and width of the 2D pooling window.
+        It determines how much the input is downsampled along each dimension.
+        An integer or a tuple of two integers specifying the stride length for 
+        moving the pooling window across the input. If `None`, it defaults to 
+        `pool_size`.
+        One of `"valid"` or `"same"`. When set to `"valid"`, no padding is applied 
+        and the output size is reduced. When set to `"same"`, appropriate padding 
+        is added so that the output dimensions match the input dimensions.
+        String specifying the ordering of the dimensions in the inputs. If `None`,
+        it defaults to the backend's default format. The two possible formats are:
+        Additional arguments passed through to the parent `Pooling2D` class.
+    Usage:
+    ------
+    The `MaxPooling2D` layer can be integrated into a neural network model to 
+    reduce spatial dimensions by selecting the maximum value over specified windows.
+    Example:
+    --------
+    ```python
+    # Define a simple CNN model with max pooling
+    model = Sequential([
+        Conv2D(32, (3, 3), activation='relu', input_shape=(28, 28, 1)),
+        MaxPooling2D(pool_size=(2, 2))
+    ])
+    # Compile the model
+    model.compile(optimizer='adam', loss='sparse_categorical_crossentropy', metrics=['accuracy'])
+    ```
+    This example demonstrates how to use `MaxPooling2D` following a convolutional 
+    layer in a model. It effectively reduces spatial dimensions while retaining 
+    important features from the input data.
+    Notes:
+    ------
+    - Ensure that input data is preprocessed appropriately, such as normalization.
+    - Understand how different padding strategies (`'valid'` vs `'same'`) affect 
+      the output size of your layer.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -13092,7 +14307,35 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Performs 3D max pooling over an input data tensor along its depth, height, and width.
+    -----------------------
+    The `MaxPooling3D` class is a subclass of `Pooling3D`, designed to apply a 
+    3-dimensional max pooling operation on input data. This operation partitions the 
+    input into non-overlapping rectangular sub-regions, and for each sub-region, it 
+    outputs the maximum value found within that region.
+    Max pooling reduces the spatial dimensions (depth, height, width) of the input 
+    tensor while retaining the most prominent features in each sub-region. This class 
+    leverages PyTorch's `nn.max_pool3d` function to perform this operation efficiently,
+    which is particularly useful for reducing computation and controlling overfitting
+    in deep learning models that process 3D data.
+    ---------------------------------
+    __init__(self, pool_size=(2, 2, 2), strides=None, padding='valid', data_format=None, **kwargs)
+          the pooling operation for each dimension. If None, it defaults to `pool_size`.
+          'Same' will pad input such that output has the same length as the original input.
+          Default is None which infers from the input shape.
+    -------------------------------------
+    This class can be used for performing max pooling operations on 3D data, such as in 
+    volumetric image processing or video analysis. It is crucial to ensure that input 
+    dimensions match the expected format by setting `data_format` accordingly.
+    Example usage:
+        &gt;&gt;&gt; import torch
+        &gt;&gt;&gt; from my_module import MaxPooling3D  # Assuming this class is part of a module named 'my_module'
+        &gt;&gt;&gt; max_pooling_layer = MaxPooling3D(pool_size=(2, 2, 2))
+        &gt;&gt;&gt; output_tensor = max_pooling_layer(input_tensor)
+    Note: The `MaxPooling3D` layer is typically used in convolutional neural networks 
+          where it helps to reduce the computational load and control overfitting by 
+          down-sampling the input data. Ensure compatibility with other layers by 
+          correctly configuring input shapes and parameters.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -13519,7 +14762,46 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Metric Class
+The `Metric` class is a base class for defining custom metrics in Keras, intended to be used within machine learning models to track performance measures such as accuracy, precision, etc. This class provides essential methods and properties that can be overridden by subclasses to implement specific metric calculations.
+Attributes:
+Methods:
+    __init__(self, dtype=None, name=None):
+        Initializes the Metric class with optional data type and name. The `name` parameter can be set manually or automatically derived from the class name. The `_dtype_policy` determines how data types are handled during computations, and a list of variables and metrics is maintained for state management.
+    reset_state(self):
+        Resets all tracked variables to zero in preparation for new computations. This method iterates over each variable associated with the metric and assigns it an array of zeros with the same shape and dtype as the original variable.
+    update_state(self, *args, **kwargs):
+        Abstract method that must be implemented by subclasses to define how the metric's state is updated based on new data inputs during model training or evaluation.
+    stateless_update_state(self, metric_variables, *args, **kwargs):
+        Updates the metric's state without modifying internal variables directly. It requires `metric_variables` to match one-to-one with the metric's variables in length and type. A `StatelessScope` is used to manage variable states during the update.
+    result(self):
+        Abstract method that must be implemented by subclasses to compute and return the current result based on the updated state.
+    stateless_result(self, metric_variables):
+        Computes the metric's result using provided tensors (`metric_variables`) without altering internal variables. Ensures that `metric_variables` matches the length of the metric's variables and uses a `StatelessScope` for computation.
+    stateless_reset_state(self):
+        Resets the metric's state in a stateless manner, returning new values for tracked variables. Uses a `StatelessScope` to manage variable states during reset.
+    dtype(self):
+        Returns the computed data type of the metric based on the `_dtype_policy`.
+    _obj_type(self):
+        Returns the string 'Metric' indicating the object type.
+    add_variable(self, shape, initializer, dtype=None, aggregation='sum', name=None):
+        Adds a new variable to the metric with specified properties. Ensures that `super().__init__()` is called in subclass constructors before adding variables.
+    variables(self):
+        Returns all variables associated with the metric, including those from nested metrics. Aggregates variables from both direct and nested metrics for comprehensive tracking.
+    __call__(self, *args, **kwargs):
+        Updates state and returns the result of the metric computation. Ensures that `super().__init__()` is called in subclass constructors before performing operations.
+    get_config(self):
+        Generates a configuration dictionary containing the name and data type of the metric for serialization purposes.
+    from_config(cls, config):
+        Restores an instance of the Metric class from a configuration dictionary. This method facilitates easy deserialization to recreate the metric with the same properties as defined in the configuration.
+    __setattr__(self, name, value):
+        Tracks attribute assignments if `_tracker` is present by leveraging its `track` method before assigning values using `super().__setattr__()`.
+    _check_super_called(self):
+        Ensures that `super().__init__()` was called in the subclass's constructor. Raises a RuntimeError if this initialization step is missed, promoting correct base class setup.
+    __repr__(self):
+        Returns a string representation of the metric for debugging and logging purposes, indicating its name and type.
+    __str__(self):
+        Provides an alias to `__repr__` for convenience in obtaining a textual description of the metric.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -13949,7 +15231,36 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A transformer that converts multilabel inputs to binary label indicators.
+    The `MultiLabelBinarizer` class is designed for transforming lists of multi-labels 
+    (or arrays with multiple columns) into a binary matrix indicating the presence or 
+    absence of each label. This transformation can be performed using separate `fit` and 
+    `transform` methods, or combined using `fit_transform`.
+    Attributes:
+            Holds the unique labels that occur in the input data.
+            Whether to output a scipy.sparse matrix (CSR format). Default is False.
+    Parameters:
+            The set of possible labels. If None, these will be determined from the input data.
+            If True, returns a sparse binary indicator matrix with CSR format.
+    Methods:
+        fit(y) -&gt; self
+            Fit label binarizer according to y in a multi-label classification setup.
+        fit_transform(y) -&gt; yt
+            Fit label binarizer and transform y in one step.
+        transform(y)
+            Transform new labels to binary format using the fitted classes.
+        inverse_transform(yt)
+            Convert the binary matrix back into a list of lists of labels.
+    Raises:
+                    transformation does not match the expected format (e.g., non-binary values).
+    Example:
+        &gt;&gt;&gt; from sklearn.preprocessing import MultiLabelBinarizer
+        &gt;&gt;&gt; mlb = MultiLabelBinarizer()
+        &gt;&gt;&gt; mlb.fit([['chocolate', 'strawberry'], ['vanilla']])
+        MultiLabelBinarizer(...)
+        &gt;&gt;&gt; mlb.transform([['chocolate', 'mint'], ['vanilla']])
+        array([[1, 0, 0],
+               [0, 0, 1]])</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -15111,7 +16422,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>OneHotEncoder is designed to transform categorical variables into a one-hot encoded format.
+    This encoder processes each categorical feature with `n` categories by converting them 
+    into `n` binary features, indicating the presence or absence of each category. It supports 
+    handling unknown categories and provides options to drop specific categories during transformation.
+    Parameters
+    ----------
+        Determines if the encoder should automatically identify unique values in each column ('auto')
+        or use a predefined list of categories for each feature.
+        Specifies which category to drop. Options include:
+        - An array-like of values indicating specific categories to drop for each feature.
+        If True, returns a sparse matrix representation of the encoded features.
+        Desired data type of the output. Must be a floating point type if `sparse_output` is False.
+        Determines how to handle unknown categories encountered during transformation:
+        Minimum frequency threshold for a category to be included. If None, all categories are included.
+        Maximum number of categories per feature. Exceeding categories will be treated as 'infrequent'.
+        Method to combine feature names and category values:
+        - A custom callable that takes a feature name and a category value and returns a string.
+    Attributes
+    ----------
+        The identified categories for each feature determined during fitting.
+        Indices of the categories that are dropped for each feature.
+        Number of output features per input feature after encoding.
+    Methods
+    -------
+    fit(X, y=None)
+        Determines the unique categories in the data and prepares the encoder based on them.
+    transform(X)
+        Converts the input data into a one-hot encoded format using the fitted encoder.
+    inverse_transform(X)
+        Reverts the one-hot encoded data back to its original categorical representation.
+    get_feature_names_out(input_features=None)
+        Provides output feature names for transformation.
+    Notes
+    -----
+    - The encoder can manage missing values and infrequent categories according to specified parameters.
+    - It supports both dense and sparse matrix outputs.
+    Examples
+    --------
+    &gt;&gt;&gt; from sklearn.preprocessing import OneHotEncoder
+    &gt;&gt;&gt; enc = OneHotEncoder()
+    &gt;&gt;&gt; X = [['Male'], ['Female'], ['Female']]
+    &gt;&gt;&gt; enc.fit(X)
+    OneHotEncoder(...)
+    &gt;&gt;&gt; enc.transform([['Female'], ['Male']])
+    array([[0., 1.],
+           [1., 0.]])</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -15615,7 +16971,65 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Parameters
+    ----------
+        The number of samples (or proportion of total samples) required to form a dense region (core point). Must be &gt;= 2.
+        Maximum distance between two points for them to be considered neighbors. Used when `cluster_method='dbscan'`.
+        The distance metric used to compute distances between instances in the feature array. Must be one of the options defined in `_VALID_METRICS` or a callable.
+        Parameter for the Minkowski metric when `metric='minkowski'`. Should be &gt;= 1.
+        Additional keyword arguments for the metric function.
+        Method used for hierarchical clustering. 'xi' uses a minimum steepness approach, while 'dbscan' is similar to DBSCAN using reachability distances.
+        The maximum distance between two samples for one to be considered as in the neighborhood of the other when `cluster_method='dbscan'`. If None, uses `max_eps`.
+        Minimum steepness on reachability plot required to form a cluster when using 'xi'.
+        Whether to apply predecessor correction for clustering.
+        The minimum number of samples in a cluster (or proportion of total samples). If None, defaults to `min_samples`.
+        Algorithm used to compute the nearest neighbors. See NearestNeighbors for details.
+        Leaf size passed to BallTree or KDTree algorithms. Affects performance and memory usage.
+        Used to cache the distance matrix between instances in a call to `fit`. By default, no caching is done. If an instance of joblib.Memory is passed, caching is enabled.
+        The number of parallel jobs to run for neighbors search. None means 1 unless in a joblib.parallel_backend context.
+    Attributes
+    ----------
+        The order in which the points are processed by the algorithm.
+        Core distances of each point, used to determine reachability distance.
+        Reachability distances for each point.
+        Predecessors in the order array.
+        Cluster labels assigned to each point, with -1 indicating noise.
+        If `cluster_method='xi'`, this attribute contains a hierarchy of clusters formed by OPTICS.
+    Methods
+    -------
+    fit(X, y=None)
+        Fit the model to data matrix X. This method estimates the parameters using X and stores the results in the object.
+        Parameters
+        ----------
+            The input data to be clustered. Can be a dense numpy array or a scipy sparse matrix.
+            Ignored as OPTICS is unsupervised. It exists only for compatibility with sklearn pipeline.
+        Returns
+        -------
+            Fitted estimator.
+    Notes
+    -----
+    - The algorithm supports different metrics for distance computation, including 'minkowski', 'euclidean', and others specified in `_VALID_METRICS`.
+    - Sparse matrices are supported but may incur efficiency warnings if used with certain configurations.
+    - If the metric requires boolean data and the input is not boolean, a warning will be issued.
+    Warnings
+    --------
+    - A `DataConversionWarning` is raised if the data type needs conversion for the chosen metric.
+    - A `SparseEfficiencyWarning` may occur when using sparse matrices.
+    Examples
+    --------
+    ```python
+    # Sample data
+    X = np.array([[1, 2], [2, 3], [3, 4], [8, 7], [8, 8], [25, 80]])
+    # Create an instance of OPTICS
+    optics_model = OPTICS(min_samples=2)
+    # Fit the model to data
+    optics_model.fit(X)
+    # Access the labels
+    print(optics_model.labels_)
+    ```
+    References
+    ----------
+    - Ester, M., Kriegel, H. P., Sander, J., &amp; Xu, X. (1996). A Density-Based Algorithm for Discovering Clusters in Large Spatial Databases with Noise. In Proceedings of the 2nd International Conference on Knowledge Discovery and Data Mining.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -16272,7 +17686,31 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>The `OrdinalEncoder` class is designed to encode categorical features as ordinal integers. This encoding process assigns an integer value to each category based on either the order of frequency or other characteristics such as their impact on a target variable.
+    Attributes:
+        categories (array-like of shape (n_features,) or 'auto', default='auto'):
+            Specifies the categories to encode for each feature. It can be set to `'auto'` to automatically determine categories from the data, a list of unique categories per feature, or a single category list if all features share the same categories.
+        dtype (data-type, default=np.float64):
+            The data type of the encoded output, allowing control over precision and storage requirements for transformed data.
+        handle_unknown (str, {'error', 'use_encoded_value'}, default='error'):
+            Determines how to handle unknown categories encountered during transformation:
+        unknown_value (int or np.nan or None, default=None):
+            The value used for encoding unknown categories when `handle_unknown` is set to `'use_encoded_value'`. It must be an integer or `np.nan`. If `None`, it defaults to one more than the maximum of the encoded values.
+        encoded_missing_value (scalar or np.nan, default=np.nan):
+            The value used for encoding missing values in the input data. For non-float dtypes, any scalar is valid; for float dtypes, `np.nan` can be used to represent missing values.
+        min_frequency (int or float or None, default=None):
+            Sets a minimum frequency threshold for categories not to be considered infrequent. An integer represents the minimum count of occurrences, while a float indicates a fraction of total occurrences needed.
+        max_categories (int or None, default=None):
+            Limits the number of categories per feature before they are deemed infrequent. If exceeded, additional categories might be treated as 'infrequent'.
+    Methods:
+        __init__(*, categories='auto', dtype=np.float64, handle_unknown='error', unknown_value=None, encoded_missing_value=np.nan, min_frequency=None, max_categories=None):
+            Initializes the OrdinalEncoder with specified parameters.
+        fit(X[, y]):
+            Learns the category encodings from input data `X`. Raises a `ValueError` if `unknown_value` is np.nan and dtype is not float when `handle_unknown` is 'use_encoded_value'.
+        transform(X):
+            Transforms the input data `X` using learned category mappings, handling missing values and unknown categories as specified.
+        inverse_transform(X):
+            Reverses the encoding to recover original categorical values from encoded data. Returns `None` for unknown values and `'infrequent_sklearn'` for infrequent categories if applicable.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -16444,7 +17882,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A 1D pooling layer that performs spatial down-sampling operations along the temporal dimension 
+    of input data. This class provides a flexible way to apply different types of pooling functions, 
+    which are critical for reducing the size and complexity of inputs in neural network models.
+    Parameters:
+    ----------
+        The function used for pooling. It must accept arguments such as inputs, pooling window size, strides,
+        padding type, and data format. Common examples include max pooling or average pooling functions.
+        Size of the window over which to perform the pooling operation. This can be a single integer (applied uniformly)
+        or a tuple/list containing one integer specifying the dimension size.
+        Strides between successive pooling windows. If not specified, it defaults to `pool_size`. It can also be 
+        an integer or a tuple/list with one integer value.
+        Type of padding algorithm to use. Options are `"valid"` (no padding) and `"same"` (zero-padding to maintain output size). 
+        Defaults to `"valid"`.
+        The ordering of dimensions in the input data. Options are `channels_last` (default) for inputs with shape 
+        `(batch_size, steps, features)` and `channels_first` for inputs with shape `(batch_size, features, steps)`.
+        An optional name for this layer instance, which can be useful for model debugging or serialization.
+        Additional parameters passed to the parent Layer class during initialization.
+    Methods:
+    -------
+    call(inputs)
+        Executes the pooling operation by applying `pool_function` over the inputs. It expands input dimensions 
+    compute_output_shape(input_shape)
+        Computes and returns the shape of the layer's output given an input shape. This method considers the effects
+        of padding, strides, and pool size on the spatial dimensions of the output.
+    get_config()
+        Returns a dictionary containing the configuration parameters of the layer, allowing it to be serialized or 
+        reconstructed later with the same settings.
+    Overall Purpose:
+    -------
+    The `Pooling1D` class is designed for down-sampling operations across the temporal dimension in sequence-based data.
+    By supporting various pooling functions and offering flexible parameterization, this layer helps reduce spatial 
+    dimensions and computational costs within models handling sequential or time-series data.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -16635,7 +18104,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>2D Pooling layer.
+    This class implements a pooling operation over the spatial dimensions (height and width) of an input tensor,
+    typically used to downsample feature maps in convolutional neural networks. It supports different types 
+    of pooling operations such as max pooling, average pooling, etc., by accepting a custom pooling function.
+    Attributes:
+                       This function should accept `ksize`, `strides`, `padding`, and `data_format` as parameters.
+                   (vertical, horizontal). If an integer is provided, it will be used for both dimensions.
+                 Defaults to `pool_size` if not provided.
+                 `"same"` results in padding the input such that the output has the same height/width dimension as the original input.
+                     of dimensions in the inputs. `channels_last` corresponds to inputs with shape 
+                     `(batch_size, ..., channels)` while `channels_first` corresponds to `(batch_size, channels, ...)`.
+    Methods:
+        __init__(self, pool_function, pool_size, strides=None, padding='valid', data_format=None, name=None, **kwargs):
+            Initializes a new instance of Pooling2D.
+        call(self, inputs):
+            Applies the pooling operation on the input tensor and returns the result.
+        compute_output_shape(self, input_shape):
+            Computes and returns the output shape of the layer given an input shape.
+        get_config(self):
+            Returns the configuration of this layer as a dictionary.
+    Example:
+        ```
+        # Create a Pooling2D layer with max pooling
+        pooling_layer = Pooling2D(pool_function=MaxPooling2D, pool_size=(2, 2), strides=(2, 2), padding='valid', data_format='channels_last')</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -16839,7 +18331,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A custom 3D pooling layer designed for use in convolutional neural networks (CNNs) with TensorFlow's Keras API. 
+    This layer applies a specified pooling function to the input data, reducing its spatial dimensions while preserving important features.
+    Attributes:
+                                  If a single integer is provided, it will be used for all dimensions.
+                       `"same"` pads the input such that the output has the same length as the original input.
+                           `channels_last` corresponds to inputs with shape `(batch_size, depth, height, width, channels)`, while 
+                           `channels_first` corresponds to `(batch_size, channels, depth, height, width)`.
+    Methods:
+        __init__(self, pool_function, pool_size, strides=None, padding='valid', data_format='channels_last', name=None, **kwargs):
+            Initializes a Pooling3D layer instance with specified pooling parameters.
+        call(self, inputs):
+            Applies the pooling operation to the input tensor and returns the pooled output. Handles transposing of inputs 
+        compute_output_shape(self, input_shape):
+            Computes the shape of the output based on the input shape, taking into account padding and strides.
+        get_config(self):
+            Returns the configuration of the layer as a dictionary, which can be used for serializing the model.
+    Usage:
+        ```python
+        # Example usage with a max pooling function
+        pooling_layer = Pooling3D(pool_function=tf.nn.max_pool3d, pool_size=(2, 2, 2), strides=(1, 1, 1))
+        input_tensor = tf.random.normal((1, 10, 10, 10, 3))  # Example input tensor
+        output = pooling_layer(input_tensor)
+        ```
+    Raises:
+    Examples:
+        ```python
+        # Define a 3D input tensor with shape (batch_size, depth, height, width, channels)
+        inputs = tf.random.normal((2, 8, 8, 8, 4))
+        # Create a Pooling3D layer with max pooling
+        pooling_layer = Pooling3D(pool_function=tf.nn.max_pool3d, pool_size=(2, 2, 2), strides=(1, 1, 1))
+        # Apply the pooling operation to the input tensor
+        pooled_output = pooling_layer(inputs)
+        ```
+    Notes:
+        - Ensure that TensorFlow is installed and available as `tf`.
+        - The `pool_function` should be compatible with the input tensor dimensions.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -17169,7 +18696,73 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initializes a PCA model with specified parameters.
+        Parameters:
+        Raises:
+        """
+        valid_solver = {'eigen', 'svd'}
+            raise AttributeError(f'Must be in {valid_solver}. Found {solver}')
+            raise AttributeError('n_components must be &gt; 1 or None')
+        """
+        Fits the PCA model to the data X.
+        Parameters:
+        Returns:
+        """
+        """
+        Internal method to compute PCA decomposition and related attributes.
+        Parameters:
+        Returns:
+        Note:
+            This method is intended for internal use within the class.
+        """
+        n_samples = X.shape[0]
+        n_features = X.shape[1]
+            n_components = n_features
+        else:
+            n_components = self.n_components
+            cov_mat = self._covariance_matrix(X)
+        elif self.solver == 'svd':
+        tot = np.sum(self.e_vals_)
+        """
+        Transforms the dataset X into its principal components using the fitted model.
+        Parameters:
+        Returns:
+        Raises:
+        """
+            raise AttributeError('Object as not been fitted, yet.')
+        transformed = X.dot(self.w_)
+            transformed = norm.dot(transformed.T).T
+        """
+        Internal method to compute covariance matrix of the input data.
+        Parameters:
+        Returns:
+        Note:
+            This method is intended for internal use within the class.
+        """
+        mean_vec = np.mean(X, axis=0)
+        cov_mat = (X - mean_vec).T.dot(X - mean_vec) / (X.shape[0] - 1)
+        """
+        Internal method to perform eigenvalue or SVD decomposition.
+        Parameters:
+        Returns:
+        Note:
+            This method is intended for internal use within the class.
+        """
+            e_vals, e_vecs = sp.linalg.eig(mat)
+        elif self.solver == 'svd':
+            mat_centered = mat - mat.mean(axis=0)
+            u, s, _ = sp.linalg.svd(mat_centered.T, lapack_driver='gesvd')
+            e_vecs, e_vals = (u, s)
+            e_vals = e_vals ** 2 / (n_samples - 1)
+                new_e_vals = np.zeros(e_vecs.shape[1])
+                e_vals = new_e_vals
+        """
+        Internal method to compute loadings.
+        Returns:
+        Note:
+            This method is intended for internal use within the class.
+        """</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -17595,7 +19188,44 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>RMSprop Optimizer Class
+This class implements the RMSprop optimization algorithm, which is designed to adaptively adjust learning rates for each parameter. It's particularly useful for training deep neural networks.
+Attributes:
+Methods:
+__init__(self, learning_rate=0.001, rho=0.9, momentum=0.0, epsilon=1e-07, centered=False, name='RMSprop', **kwargs)
+    Initializes the RMSprop optimizer with specified hyperparameters.
+    Parameters:
+        learning_rate (float, default=0.001): 
+            The step size at each iteration while moving toward a minimum of the loss function. It controls how much to adjust the model in response to the estimated error each time the weights are updated.
+        rho (float, default=0.9): 
+            A decay rate for the moving average of squared gradients. This parameter is used to compute the exponentially weighted average of past squared gradients, helping to stabilize the learning process.
+        momentum (float or callable, default=0.0): 
+            The momentum factor applied to previous updates. If a float, it must be between 0 and 1. A value greater than 0 applies momentum to speed up convergence by accelerating along relevant directions.
+        epsilon (float, default=1e-07): 
+            A small constant added for numerical stability to prevent division by zero during the update step.
+        centered (bool, default=False): 
+            If True, computes the centered RMSprop update, which normalizes the gradient by a moving average of its variance. This can sometimes lead to more stable and faster convergence.
+        name (str, default='RMSprop'): 
+            Optional name prefix for the operations created when applying gradients.
+        **kwargs: 
+            Additional keyword arguments that may include learning rate decay or other optimizer settings.
+    Raises:
+_create_slots(self, var_list)
+    Creates additional variables (slots) required for the optimizer to store intermediate values.
+    Parameters:
+_prepare_local(self, var_device, var_dtype, apply_state)
+    Prepares local computations for applying gradients to variables.
+    Parameters:
+_resource_apply_dense(self, grad, var, apply_state=None)
+    Applies dense gradient updates to variables using RMSprop logic.
+    Parameters:
+_resource_apply_sparse(self, grad, var, indices, apply_state=None)
+    Applies sparse gradient updates to variables using RMSprop logic.
+    Parameters:
+_set_weights(self, weights)
+    Sets optimizer's weights from a provided list of values.
+get_config(self)
+    Returns the configuration dictionary for this optimizer instance.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -18334,7 +19964,51 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>SelfTrainingClassifier implements a self-training mechanism for semi-supervised learning.
+    This classifier starts with a small labeled dataset and iteratively labels the unlabeled data points based on model predictions. It uses a base estimator to classify samples, gradually expanding its training set by adding confidently predicted samples from the unlabeled pool into the labeled dataset. The process continues until a stopping criterion is met.
+    Parameters
+    ----------
+        The base estimator to use for self-training. If None, `base_estimator` must be provided.
+        A fitted classifier with methods `fit`, `predict_proba`. Use of this parameter is discouraged in favor of `estimator`.
+        The probability threshold for labeling a sample confidently. Samples with predicted probabilities above this threshold are considered confident and added to the labeled set.
+        Criterion used for selecting samples during each iteration:
+        Number of unlabeled samples to label per iteration when using the 'k_best' criterion.
+        Maximum number of iterations for self-training. If None, iterates until all samples are labeled.
+        If True, prints progress information at each iteration.
+    Attributes
+    ----------
+        The fitted base estimator after the completion of self-training.
+        Class labels known to the classifier after training.
+        Transduced labels for all samples, including those initially unlabeled.
+        Iteration number at which each sample was first labeled.
+        Number of iterations performed during self-training.
+    Methods
+    -------
+    fit(X, y) -&gt; SelfTrainingClassifier
+        Fit the model using X as training data and y as target values.
+    predict(X) -&gt; ndarray of shape (n_samples,)
+        Perform classification on samples in X.
+    predict_proba(X) -&gt; ndarray of shape (n_samples, n_classes)
+        Return probability estimates for each class for test vector X.
+    decision_function(X) -&gt; ndarray
+        Compute the distance or difference between samples and decision boundary.
+    predict_log_proba(X) -&gt; ndarray of shape (n_samples, n_classes)
+        Return log-probability estimates for each class for test vector X.
+    score(X, y) -&gt; float
+        Returns the mean accuracy on the given test data and labels.
+    Notes
+    -----
+    - `base_estimator` is deprecated as of version 1.6 and will be removed in version 1.8.
+    - This classifier is suitable for semi-supervised learning where only a small portion of the dataset is labeled initially.
+    _allowed_values
+    ----------------
+        The estimator must be either `None` or an object with a `fit` method. If `None`, `base_estimator` is used.
+        Deprecated parameter; should have methods `fit`. Use `estimator` instead. Allowed values are hidden under the deprecated option 'deprecated'.
+        A float value representing the probability threshold for labeling a sample confidently. Must be in the interval [0.0, 1.0).
+        Criterion used for selecting samples during each iteration. Allowed values are 'threshold' or 'k_best'.
+        An integer specifying the number of unlabeled samples to label per iteration when using the 'k_best' criterion. Must be at least 1.
+        Maximum number of iterations for self-training. Can be an integer &gt;= 0 or `None` for no limit.
+        If set to 'verbose', prints progress information during training.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -18593,7 +20267,38 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>----------------
+SeparableConv
+Constructor (`__init__`) Docstring:
+-----------------------------------
+__init__(self, rank, filters, kernel_size, strides=1, padding='valid', data_format=None, dilation_rate=1, depth_multiplier=1, activation=None, use_bias=True, depthwise_initializer='glorot_uniform', pointwise_initializer='glorot_uniform', bias_initializer='zeros', depthwise_regularizer=None, pointwise_regularizer=None, bias_regularizer=None, activity_regularizer=None, depthwise_constraint=None, pointwise_constraint=None, bias_constraint=None, trainable=True, name=None, **kwargs)
+    Initializes a SeparableConv layer.
+    Parameters:
+`build` Method Docstring:
+-------------------------
+build(self, input_shape)
+    Builds the layer by initializing its weights and biases based on the provided input shape.
+    Parameters:
+    Raises:
+    Details:
+        - Validates the input shape, ensuring that the channel axis has a defined size.
+        - Calculates and initializes depthwise and pointwise kernels based on the layer configuration.
+        - Adds bias variables if `use_bias` is set to True.
+`call` Method Docstring:
+------------------------
+call(self, inputs)
+    Performs the forward pass of the SeparableConv layer.
+    Parameters:
+    Raises:
+`get_config` Method Docstring:
+-----------------------------
+get_config(self)
+    Returns a configuration dictionary containing all parameters necessary to recreate the SeparableConv layer instance.
+    Returns:
+General Notes:
+--------------
+- The `build` method may raise a ValueError if input shapes are not as expected.
+- Assumptions include defined channel dimensions in input shapes.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -18871,7 +20576,26 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Class SeparableConv1D
+The `SeparableConv1D` class provides a specialized implementation of separable convolution specifically for 1-dimensional data inputs, such as time series or sequences. It extends from its parent class `SeparableConv`, adapting it to perform depthwise and pointwise convolutions on 1D data efficiently.
+Attributes:
+Initialization Parameters:
+Methods:
+    __init__(self, filters, kernel_size, strides=1, padding='valid', data_format=None, dilation_rate=1, depth_multiplier=1, activation=None, use_bias=True, depthwise_initializer='glorot_uniform', pointwise_initializer='glorot_uniform', bias_initializer='zeros', depthwise_regularizer=None, pointwise_regularizer=None, bias_regularizer=None, activity_regularizer=None, depthwise_constraint=None, pointwise_constraint=None, bias_constraint=None, **kwargs)
+        Initializes the SeparableConv1D layer with specified configurations.
+    call(self, inputs)
+        Performs the separable convolution operation on the input data.
+        Parameters:
+                    (batch_size, input_dim, steps) for 'channels_first'.
+        Returns:
+            Tensor resulting from applying the separable convolution and any specified activation function.
+Additional Information:
+- The class is designed to handle 1D sequential data, making it suitable for applications like time series analysis.
+- Ensure that input dimensions are compatible with kernel size, strides, and padding settings.
+- Using 'causal' padding requires careful consideration of sequence length to ensure correct causal behavior.
+Dependencies:
+- Relies on TensorFlow's backend functions such as `separable_conv2d`, `bias_add`, and various initializers,
+  regularizers, and constraints.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -19128,7 +20852,16 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Separable 2D Convolution Layer
+    The `SeparableConv2D` class extends the `SeparableConv` base class to implement a separable convolutional layer for 2D inputs. This variant of standard convolutions is more efficient by decomposing them into depthwise and pointwise operations.
+    Attributes:
+    Parameters:
+    Returns:
+        None
+    Raises:
+    Methods:
+            Parameters:
+            Returns:</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -20410,7 +22143,65 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Sequential Feature Selector.
+    This class implements a sequential feature selection algorithm. It selects features based on their 
+    contribution to the performance of an estimator using either forward or backward search strategies,
+    the selection process.
+    Attributes
+    ----------
+        The base estimator from which the feature selector is built.
+        Number of features to select. It can be a positive integer, a tuple (min, max), or one of the 
+        strings "best" or "parsimonious".
+        Whether to perform forward selection.
+        Whether to allow floating search.
+        Controls the number of jobs that get dispatched during parallel execution. Useful for managing 
+        memory consumption by reducing job count if necessary.
+        Verbosity level.
+        A single string (see model evaluation documentation) or a callable (see sklearn.metrics documentation)
+        to evaluate the predictions on the test set. If None, defaults based on estimator type.
+        Determines the cross-validation splitting strategy.
+        Number of jobs to run in parallel for fit. -1 uses all processors.
+        Whether to clone the estimator for each feature subset evaluation.
+        Indices or names of features that are always included in the selected subsets.
+        A list where each sublist represents a group of features. Features within the same group must be 
+        either all selected or none selected.
+    Methods
+    -------
+    fit(X, y, groups=None, **fit_params)
+        Fit the SequentialFeatureSelector to data.
+    transform(X)
+        Transform X by selecting features based on the fitted model.
+    fit_transform(X, y, groups=None, **fit_params)
+        Fit to data, then transform it.
+    get_metric_dict(confidence_interval=0.95)
+        Get a dictionary with metrics for each subset of features evaluated during fitting.
+    named_estimators
+        Property that returns the name of the estimator used in the feature selector.
+    get_params(deep=True)
+        Get parameters for this estimator.
+    set_params(**params)
+        Set the parameters for this estimator.
+    Raises
+    ------
+    TypeError
+        If `cv` is a generator object.
+    ValueError
+        If there are inconsistencies in fixed features or feature groups.
+    AttributeError
+        For various attribute-related errors such as invalid `k_features`, mismatched types, etc.
+    Example
+    -------
+    &gt;&gt;&gt; from sklearn.datasets import load_iris
+    &gt;&gt;&gt; from sklearn.linear_model import LogisticRegression
+    &gt;&gt;&gt; from sklearn.feature_selection import SequentialFeatureSelector
+    &gt;&gt;&gt; X, y = load_iris(return_X_y=True)
+    &gt;&gt;&gt; estimator = LogisticRegression()
+    &gt;&gt;&gt; sfs = SequentialFeatureSelector(estimator, n_features_to_select=2)
+    &gt;&gt;&gt; sfs.fit(X, y)
+    Notes
+    -----
+    The `SequentialFeatureSelector` can be used with any scikit-learn compatible estimator. It supports both 
+    classification and regression tasks.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -20687,7 +22478,40 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Stochastic Gradient Descent (SGD) Optimizer
+    Implements the Stochastic Gradient Descent optimization algorithm, which is widely used for training machine learning models. 
+    This optimizer supports optional momentum and Nesterov acceleration to potentially enhance convergence speed.
+    Attributes:
+    Methods:
+    __init__(self, learning_rate=0.01, momentum=0.0, nesterov=False, name='SGD', **kwargs)
+        Initializes the SGD optimizer with specified parameters.
+        Parameters:
+                                               thus leading to faster converging. Must be between [0, 1]. Default is 0.0.
+        Raises:
+    _create_slots(self, var_list)
+        Creates additional variables (slots) used in optimization, such as momentum buffers.
+        Parameters:
+        This method prepares the optimizer to store state information needed for applying updates.
+    _prepare_local(self, var_device, var_dtype, apply_state)
+        Prepares local state variables before applying gradients.
+        Parameters:
+        Ensures that necessary hyperparameters are set correctly on the device and dtype level.
+    _resource_apply_dense(self, grad, var, apply_state=None)
+        Applies dense gradient updates to the variable `var`.
+        Parameters:
+        Uses either Keras Momentum or standard Gradient Descent based on whether momentum is enabled.
+    _resource_apply_sparse_duplicate_indices(self, grad, var, indices, **kwargs)
+        Handles sparse gradient updates with duplicate indices.
+        Parameters:
+        Ensures that updates are applied correctly even when the same index is encountered multiple times in a batch.
+    _resource_apply_sparse(self, grad, var, indices, apply_state=None)
+        Applies sparse gradient updates to the variable `var`.
+        Parameters:
+        Similar to `_resource_apply_dense`, but optimized for sparse data.
+    get_config(self)
+        Returns a dictionary containing the configuration of the optimizer.
+        This is useful for serializing the optimizer's state, which is essential for saving and loading models.
+        Returns:</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -21011,7 +22835,78 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initializes the SoftmaxRegression model with specified hyperparameters.
+        Parameters:
+        Returns:
+            None
+        """
+        _BaseModel.__init__(self)
+        _IterativeModel.__init__(self)
+        _Classifier.__init__(self)
+        _MultiClass.__init__(self)
+        """
+        Computes the net input by applying a linear transformation to the input data.
+        Parameters:
+        Returns:
+        """
+        """
+        Applies the softmax function to convert raw scores into probabilities.
+        Parameters:
+        Returns:
+        """
+        e_x = np.exp(z - z.max(axis=1, keepdims=True))
+        out = e_x / e_x.sum(axis=1, keepdims=True)
+        """
+        Calculates cross-entropy loss between predicted probabilities and true labels.
+        Parameters:
+        Returns:
+        """
+        """
+        Computes the cost including regularization term.
+        Parameters:
+        Returns:
+        """
+        L2_term = self.l2 * np.sum(self.w_ ** 2)
+        cross_entropy = cross_entropy + L2_term
+        """
+        Converts probability distributions into class labels by selecting the class with highest probability.
+        Parameters:
+        Returns:
+        """
+        """
+        Performs a forward pass to compute predicted probabilities for input data.
+        Parameters:
+        Returns:
+        """
+        z = self._net_input(X)
+        a = self._softmax_activation(z)
+        """
+        Calculates gradients of the loss function with respect to model parameters.
+        Parameters:
+        Returns:
+        """
+        grad_loss_wrt_out = y_true - y_probas
+        grad_loss_wrt_w = -np.dot(X.T, grad_loss_wrt_out)
+        grad_loss_wrt_b = -np.sum(grad_loss_wrt_out, axis=0)
+        """
+        Trains the model using gradient descent and updates weights and biases.
+        Parameters:
+        Returns:
+        """
+        y_enc = self._one_hot(y=y, n_labels=self.n_classes, dtype=np.float_)
+        rgen = np.random.RandomState(self.random_seed)
+                y_probas = self._forward(X[idx])
+                grad_loss_wrt_w, grad_loss_wrt_b = self._backward(X[idx], y_true=y_enc[idx], y_probas=y_probas)
+                l2_reg = self.l2 * self.w_
+            y_probas = self._forward(X)
+            cross_ent = self._cross_entropy(output=y_probas, y_target=y_enc)
+            cost = self._cost(cross_ent)
+        """
+        Predicts class probabilities for given input data.
+        Parameters:
+        Returns:
+        """</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -21724,7 +23619,155 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>}
+    @_fit_context(prefer_skip_nested_validation=True)
+        """
+        Fit the encoder using the provided data `X` and target variable `y`.
+        Computes necessary encodings based on feature-target relationships.
+        Parameters
+        ----------
+            The input samples.
+            Target values.
+        Returns
+        -------
+            Returns self.
+        """
+    @_fit_context(prefer_skip_nested_validation=True)
+        """
+        Fit to data, then transform it.
+        This method combines fitting and transforming in a single step for efficiency.
+        Parameters
+        ----------
+            The input samples.
+            Target values.
+        Returns
+        -------
+            Transformed input samples.
+        """
+        X_ordinal, X_known_mask, y_encoded, n_categories = self._fit_encodings_all(X, y)
+            cv = KFold(self.cv, shuffle=self.shuffle, random_state=self.random_state)
+        else:
+            cv = StratifiedKFold(self.cv, shuffle=self.shuffle, random_state=self.random_state)
+            X_out = np.empty((X_ordinal.shape[0], X_ordinal.shape[1] * len(self.classes_)), dtype=np.float64)
+        else:
+            X_out = np.empty_like(X_ordinal, dtype=np.float64)
+            y_train_mean = np.mean(y_train, axis=0)
+                encodings = self._fit_encoding_multiclass(X_train, y_train, n_categories, y_train_mean)
+            else:
+                encodings = self._fit_encoding_binary_or_continuous(X_train, y_train, n_categories, y_train_mean)
+        """
+        Transform the data `X` using learned encodings from fitting.
+        Useful for applying the same encoding to new datasets.
+        Parameters
+        ----------
+            The input samples.
+        Returns
+        -------
+            Transformed input samples.
+        """
+        X_ordinal, X_known_mask = self._transform(X, handle_unknown='ignore', force_all_finite='allow-nan')
+            X_out = np.empty((X_ordinal.shape[0], X_ordinal.shape[1] * len(self.classes_)), dtype=np.float64)
+        else:
+            X_out = np.empty_like(X_ordinal, dtype=np.float64)
+        """
+        Compute all necessary encodings during fitting.
+        Prepares the encoder by calculating category statistics based on the target variable.
+        Parameters
+        ----------
+            The input samples.
+            Target values.
+        Returns
+        -------
+        tuple: containing:
+                Ordinal representation of `X`.
+                Mask indicating known categories.
+                Encoded target values.
+                Number of categories for each feature.
+        """
+        check_consistent_length(X, y)
+            accepted_target_types = ('binary', 'multiclass', 'continuous')
+            inferred_type_of_target = type_of_target(y, input_name='y')
+        else:
+            label_encoder = LabelEncoder()
+            y = label_encoder.fit_transform(y)
+        elif self.target_type_ == 'multiclass':
+            label_binarizer = LabelBinarizer()
+            y = label_binarizer.fit_transform(y)
+        else:
+            y = _check_y(y, y_numeric=True, estimator=self)
+        X_ordinal, X_known_mask = self._transform(X, handle_unknown='ignore', force_all_finite='allow-nan')
+        n_categories = np.fromiter((len(category_for_feature) for category_for_feature in self.categories_), dtype=np.int64, count=len(self.categories_))
+            encodings = self._fit_encoding_multiclass(X_ordinal, y, n_categories, self.target_mean_)
+        else:
+            encodings = self._fit_encoding_binary_or_continuous(X_ordinal, y, n_categories, self.target_mean_)
+        """
+        Fit encoding specifically for binary or continuous targets.
+        Computes smoothed averages of the target values for each category.
+        Parameters
+        ----------
+            Ordinal representation of `X`.
+            Target values.
+            Number of categories for each feature.
+            Mean of the target variable.
+        Returns
+        -------
+            Encoded statistics per category.
+        """
+            y_variance = np.var(y)
+            encodings = _fit_encoding_fast_auto_smooth(X_ordinal, y, n_categories, target_mean, y_variance)
+        else:
+            encodings = _fit_encoding_fast(X_ordinal, y, n_categories, self.smooth, target_mean)
+        """
+        Fit encoding specifically for multiclass targets.
+        Calculates separate encodings for each class in a multiclass setting.
+        Parameters
+        ----------
+            Ordinal representation of `X`.
+            Target values.
+            Number of categories for each feature.
+            Mean of the target variable per class.
+        Returns
+        -------
+            Encoded statistics per category and class.
+        """
+        n_features = self.n_features_in_
+        n_classes = len(self.classes_)
+        encodings = []
+            encoding = self._fit_encoding_binary_or_continuous(X_ordinal, y_class, n_categories, target_mean[i])
+            encodings.extend(encoding)
+        reorder_index = (idx for start in range(n_features) for idx in range(start, n_classes * n_features, n_features))
+        """
+        Apply the computed encodings to ordinal data.
+        Transforms categorical features into numerical values based on precomputed encodings.
+        Parameters
+        ----------
+            Array to store transformed output.
+            Ordinal representation of `X`.
+            Mask indicating unknown categories in `X`.
+            Indices to select samples for transformation.
+            Encoded statistics per category.
+            Mean of the target variable.
+        """
+            n_classes = len(self.classes_)
+                feat_idx = e_idx // n_classes
+                mean_idx = e_idx % n_classes
+                X_out[row_indices, e_idx] = encoding[X_ordinal[row_indices, feat_idx]]
+        else:
+                X_out[row_indices, e_idx] = encoding[X_ordinal[row_indices, e_idx]]
+        """
+        Returns output feature names for transformation results.
+        Provides an array of feature names after encoding, useful for understanding transformed data.
+        Parameters
+        ----------
+            Original column names in the input dataset. If `None`, generic names will be used.
+        Returns
+        -------
+            Output feature names.
+        """
+        check_is_fitted(self, 'n_features_in_')
+        feature_names = _check_feature_names_in(self, input_features)
+            feature_names = [f'{feature_name}_{class_name}' for feature_name in feature_names for class_name in self.classes_]
+        else:</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -21999,7 +24042,53 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initializes the TransactionEncoder with no arguments.
+        Returns:
+            None
+        """
+        pass
+        """
+        Identifies unique items across all transactions in X and creates a mapping from item to column index.
+        Parameters:
+        Returns:
+        Raises:
+        """
+            raise TypeError("Input must be a list of lists.")
+        unique_items = set()
+                unique_items.add(item)
+        """
+        Converts transaction data into a binary matrix. If `sparse` is True, returns a compressed sparse row (CSR) matrix; otherwise, returns a dense NumPy array.
+        Parameters:
+        Returns:
+        Raises:
+        """
+            raise ValueError("The fit method must be called before transform.")
+            indptr = [0]
+            indices = []
+                    col_idx = self.columns_mapping_[item]
+                    indices.append(col_idx)
+                indptr.append(len(indices))
+            non_sparse_values = [True] * len(indices)
+            array = csr_matrix((non_sparse_values, indices, indptr), dtype=bool)
+        else:
+            array = np.zeros((len(X), len(self.columns_)), dtype=bool)
+                    col_idx = self.columns_mapping_[item]
+                    array[row_idx, col_idx] = True
+        """
+        Reverts the encoded binary matrix back into its original transaction form.
+        Parameters:
+        Returns:
+        Raises:
+        """
+            raise ValueError("The fit method must be called before inverse_transform.")
+        """
+        Combines fitting and transformation steps for efficiency.
+        Parameters:
+        Returns:
+        Raises:
+        """
+            raise TypeError("Input must be a list of lists.")</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -22132,7 +24221,39 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>UpSampling1D Layer
+    The `UpSampling1D` layer upsamples input data along the temporal dimension by a specified factor,
+    effectively increasing the number of time-steps in your sequence data. This is particularly useful 
+    Attributes:
+    Usage:
+        The `UpSampling1D` layer can be added to a Keras model sequentially after an input layer or 
+        another layer that outputs sequences of shape `(batch_size, timesteps, features)`. For example:
+        ```python
+        model = Sequential()
+        model.add(UpSampling1D(size=2, input_shape=(128, 64)))
+        ```
+    Note:
+        The `size` parameter must be a positive integer. The output shape of this layer will have 
+        the number of timesteps increased by the specified factor.
+    Methods:
+    __init__(self, size=2, **kwargs)
+    Initializes a new `UpSampling1D` layer.
+    Args:
+            Must be a positive integer.
+    compute_output_shape(self, input_shape)
+    Computes the output shape of the layer given an input shape.
+    Args:
+            `(batch_size, timesteps, features)`.
+    Returns:
+    call(self, inputs)
+    Performs the upsampling operation on the input tensor.
+    Args:
+            `(batch_size, timesteps, features)`.
+    Returns:
+    get_config(self)
+    Returns a dictionary containing the configuration of the layer. This includes all
+    initial arguments and their values for recreating the layer instance later.
+    Returns:</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -22334,7 +24455,26 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>**Class Summary**
+    The `UpSampling2D` class is a subclass of `Layer`, designed to perform 2D upsampling on input data. It increases the spatial dimensions (height and width) of an input tensor according to specified parameters, commonly used in convolutional neural networks for tasks such as image segmentation where higher resolution is required.
+    - `__init__(self, size=(2, 2), data_format=None, interpolation='nearest', **kwargs)`: 
+      Initializes the `UpSampling2D` layer with specified parameters and validates them. Sets up class attributes based on user input or defaults.
+    - `compute_output_shape(self, input_shape)`:
+      Computes and returns the shape of the output tensor based on the input shape and upsampling factors. Adjusts spatial dimensions according to the defined `size` attribute while maintaining other dimensions unchanged.
+      Parameters:
+      Returns:
+        - A `TensorShape` object representing the computed shape of the output tensor.
+    - `call(self, inputs)`:
+      Applies the upsampling operation to the given inputs using the specified interpolation method. This is where actual resizing occurs during the layer's forward pass.
+      Parameters:
+      Returns:
+        - A tensor with increased spatial dimensions based on the defined upsampling factors and interpolation method.
+    - `get_config(self)`:
+      Returns a dictionary containing the configuration of the layer. This is useful for saving and loading models as it captures all necessary parameters for reconstructing the layer.
+      Returns:
+        - A dictionary of the layer's configuration settings.
+    - Raises a `ValueError` if the `interpolation` argument is not one of `"nearest"` or `"bilinear"`.
+    The class relies on external modules such as `conv_utils` for data format normalization, `tensor_shape` for shape manipulation, and `backend` for performing the actual resizing operations. It also inherits from the base `Layer` class to utilize its functionalities.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -22505,7 +24645,37 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>3D Up-sampling layer that resizes a 5D tensor by specified factors along each spatial dimension.
+    The `UpSampling3D` class is designed for use in neural network architectures where increasing 
+    the resolution of 3D data is necessary, such as in volumetric data processing and medical imaging. 
+    This layer performs up-sampling by scaling the spatial dimensions (depth, height, width) of a 5D input tensor.
+    Parameters
+    ----------
+        The upsampling factors for each dimension (depth, height, width). Default is `(2, 2, 2)`. 
+        This determines how much the input tensor will be scaled along each axis.
+        One of `None`, 'channels_first', or 'channels_last'. If 'channels_first',
+        input shape should be `(batch_size, channels, depth, height, width)`.
+        If 'channels_last', input shape should be `(batch_size, depth, height, width, channels)`. 
+        Default is None, which infers the format based on the backend.
+    **kwargs
+        Additional keyword arguments passed to the base Layer class.
+    Methods
+    -------
+    __init__(size=(2, 2, 2), data_format=None, **kwargs)
+        Initializes the layer with specified upsampling size and data format.
+    compute_output_shape(input_shape)
+        Computes the output shape of the layer given an input shape. Adjusts each spatial dimension 
+        according to the specified `size` factors while keeping the batch size and channels unchanged.
+    call(inputs)
+        Performs the up-sampling operation on the input tensor using the backend's resize function.
+        Relies on TensorFlow's `resize_volumes()` method to scale the input tensor by the specified factors.
+    get_config()
+        Returns a dictionary containing the configuration of this layer for serialization purposes. 
+        Includes parameters like size and data_format, ensuring that model configurations can be saved and restored.
+    Example
+    -------
+    &gt;&gt;&gt; layer = UpSampling3D(size=(2, 2, 2), data_format='channels_last')
+    &gt;&gt;&gt; output_shape = layer.compute_output_shape(input_shape=(None, 32, 32, 32, 16))</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -22659,7 +24829,45 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>Applies zero padding to the temporal dimension of a 3D input tensor.
+    This layer is often used in neural networks, particularly convolutional neural 
+    networks, to extend the length of sequences without altering their content by 
+    adding zeros at both ends. It's especially useful for maintaining consistent sequence 
+    lengths or dimensions across layers where specific input shapes are required.
+    Attributes:
+            and end of each sequence in the input tensor. The default value is 1.
+            (batch_size, time_steps, features).
+    Methods:
+        __init__(self, padding=1, **kwargs):
+            Initializes a ZeroPadding1D instance with specified padding values. The `padding` 
+            parameter can be an integer or a tuple of two integers specifying different amounts 
+            of padding at the beginning and end of each sequence.
+        compute_output_shape(self, input_shape):
+            Computes the shape of the output tensor given an input shape. If the second dimension 
+            (time steps) of the input shape is known, it calculates the new length by adding the 
+            specified padding to both ends.
+        call(self, inputs):
+            Applies zero padding to the input tensor along its temporal axis using the specified 
+            `padding` values. This operation does not alter the batch size or feature dimension 
+            of the input tensor.
+        get_config(self):
+            Returns a dictionary containing the configuration parameters of this layer, including
+            the `padding`. It facilitates serialization of the model that contains this layer.
+    Example:
+        ```
+        # Create a ZeroPadding1D layer with 2 units of padding at both ends
+        zero_padding = ZeroPadding1D(padding=(2, 2))
+        # Assuming 'input_tensor' is a 3D tensor with shape (batch_size, time_steps, features)
+        padded_output = zero_padding(input_tensor)
+        ```
+    Input shape:
+    Output shape:
+          where `sum(padding)` is the total padding added to the temporal dimension.
+    Compatibility:
+        Compatible with Keras models and layers. Ensure that the input tensor has exactly three dimensions.
+    Notes:
+        This layer does not alter the feature or batch size dimensions of its input, 
+        only the sequence length (time steps).</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -22933,7 +25141,55 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>"""
+        Initializes the ZeroPadding2D instance with specified padding and data format.
+        Parameters:
+                                    it applies the same amount of padding to all sides.
+                                    If it's a tuple of two integers, applies symmetric padding
+                                    a tuple of two tuples can specify asymmetric padding:
+                                    ((top_pad, bottom_pad), (left_pad, right_pad)).
+                                         Defaults to None, which means the format is inferred.
+        Raises:
+        """
+        super(ZeroPadding2D, self).__init__(**kwargs)
+        elif hasattr(padding, '__len__'):
+            height_padding = conv_utils.normalize_tuple(padding[0], 2, '1st entry of padding')
+            width_padding = conv_utils.normalize_tuple(padding[1], 2, '2nd entry of padding')
+        else:
+            raise ValueError('`padding` should be either an int, a tuple of 2 ints '
+                             '(symmetric_height_pad, symmetric_width_pad), or a tuple of 2 tuples of 2 ints '
+        """
+        Computes the output shape after applying zero-padding.
+        Parameters:
+        Returns:
+        Notes:
+            - If `data_format` is 'channels_first', the dimensions are assumed to be 
+              in the order (batch_size, channels, rows, cols).
+            - If `data_format` is 'channels_last', the dimensions are assumed to be 
+              in the order (batch_size, rows, cols, channels).
+        """
+        input_shape = tensor_shape.TensorShape(input_shape).as_list()
+                rows = input_shape[2] + self.padding[0][0] + self.padding[0][1]
+            else:
+                rows = None
+                cols = input_shape[3] + self.padding[1][0] + self.padding[1][1]
+            else:
+                cols = None
+        elif self.data_format == 'channels_last':
+                rows = input_shape[1] + self.padding[0][0] + self.padding[0][1]
+            else:
+                rows = None
+                cols = input_shape[2] + self.padding[1][0] + self.padding[1][1]
+            else:
+                cols = None
+        """
+        Applies zero-padding to the input tensor.
+        Parameters:
+                             or `(batch_size, rows, cols, ...)` depending on data_format.
+        Returns:
+        Notes:
+            - This method utilizes `backend.spatial_2d_padding` to perform the padding operation.
+        """</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -23210,7 +25466,51 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>ZeroPadding3D Layer
+    This class implements a 3D padding layer that adds zeros around the input data in three dimensions. 
+    It is useful for deep learning models where spatial dimensions need to be expanded without altering 
+    the core features of the input data.
+    Attributes
+    ----------
+        The amount of zero-padding added to each dimension, specified as a single integer, a tuple of 3 integers,
+        or a tuple of 3 tuples of 2 integers.
+        Specifies the ordering of dimensions in the input data. Defaults to None, which uses the backend's default.
+    Methods
+    -------
+    __init__(self, padding=(1, 1, 1), data_format=None, **kwargs)
+        Initializes a ZeroPadding3D layer with specified padding and data format.
+    compute_output_shape(self, input_shape)
+        Computes the output shape of the layer given an input shape.
+    call(self, inputs)
+        Applies zero-padding to the input data and returns the padded result.
+    get_config(self)
+        Returns the configuration of the layer as a dictionary.
+    Parameters
+    ----------
+        The padding to add on each side. If an integer is provided, the same amount of 
+        padding is added symmetrically for all three dimensions (dim1, dim2, dim3). If a 
+        tuple with three integers is provided, it specifies the total padding along each dimension,
+        distributed equally to both sides. Alternatively, if a tuple of 3 tuples of 2 ints is given, 
+        it explicitly defines the padding as (left_pad, right_pad) for each dimension.
+        The ordering of the dimensions in the inputs. 'channels_first' corresponds to inputs with shape 
+        `(batch_size, channels, dim1, dim2, dim3)`, while 'channels_last' corresponds to inputs with shape 
+        `(batch_size, dim1, dim2, dim3, channels)`. Default is None, which uses the default image data format 
+        of the backend.
+    Returns
+    -------
+    tensor_shape.TensorShape
+        The shape of the output data after padding is applied (in `compute_output_shape` method).
+    tensor
+        The padded output data (in `call` method).
+    dict
+        A dictionary containing the layer's configuration parameters (in `get_config` method).
+    Raises
+    ------
+    ValueError
+        If `padding` does not match any of the specified types or formats.
+    Examples
+    --------
+    &gt;&gt;&gt; layer = ZeroPadding3D(padding=((1, 2), (1, 1), (0, 0)), data_format='channels_last')</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -23869,7 +26169,45 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t># ERROR: ToT Generation failed</t>
+          <t>A base class for encoding categorical features using a transformer-like approach. 
+    This class extends `TransformerMixin` and `BaseEstimator`, making it compatible with 
+    scikit-learn's pipeline structures.
+    Main Features:
+      validating the dimensionality of input arrays and checking for finite values when required.
+      transformation but were not seen during fitting, based on the `handle_unknown` parameter.
+      controlled by parameters such as `max_categories` and `min_frequency`.
+    Key Parameters:
+      will be used.
+    Methods:
+    Properties:
+    Notes:
+    - This class is typically subclassed or used directly within scikit-learn pipelines to handle 
+      categorical data preprocessing, ensuring compatibility with various machine learning algorithms.
+    """
+        """
+        Validate and preprocess the input array `X`.
+        Ensures that the input data is a two-dimensional array. If not, it validates
+        the array using scikit-learn's `check_array` function. It also ensures that the 
+        data type of the elements matches predefined types or uses object type for string data.
+        The method handles potential issues with NaN values by leveraging the `force_all_finite` parameter.
+        Parameters
+        ----------
+            The input data containing categorical features to be validated.
+            Whether to ensure that all elements in `X` are finite. If False, infinite and NaN values will be allowed.
+        Returns
+        -------
+            A list where each element is an array corresponding to a feature column from the input `X`.
+            The number of samples (rows) in the input data.
+            The number of features (columns) in the input data.
+        Raises
+        ------
+        ValueError
+            If there is a shape mismatch or if any validation checks fail, such as incompatible data types 
+            or non-finite values when `force_all_finite` is True.
+        Notes
+        -----
+        - The method handles reshaping of one-dimensional inputs to two dimensions.
+        - Ensures compatibility with pandas DataFrames by checking for the 'iloc' attribute.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
